--- a/sumki/Калькулятор_юнит-экономики_сумки.xlsx
+++ b/sumki/Калькулятор_юнит-экономики_сумки.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C37" authorId="0">
+    <comment ref="H37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -46,36 +46,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="252">
   <si>
     <t xml:space="preserve">Калькулятор юнит-экономики: онлайн-магазин женских сумок, Ташкент</t>
   </si>
   <si>
-    <t xml:space="preserve">Связан с бизнес-планом: все стартовые цифры совпадают с базовым сценарием плана (октябрь 2026).</t>
+    <t xml:space="preserve">Связан с бизнес-планом: стартовые цифры совпадают с базовым сценарием плана (октябрь 2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Как пользоваться</t>
   </si>
   <si>
-    <t xml:space="preserve">1. «Допущения» — курсы, пошлина, доставка, реклама, канал продаж, постоянные расходы. Меняйте под свои данные.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. «Юнит-экономика» — по каждой модели: закупка в юанях, розничная цена, доля в продажах. Итог — сколько остаётся с заказа и точка безубыточности.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. «Прогноз» — введите план заказов и постоянных расходов по месяцам: увидите прибыль по месяцам и окупаемость стартовых вложений.</t>
+    <t xml:space="preserve">1. «Допущения» — курсы, пошлина, доставка, реклама, канал продаж (список в ячейке B21), постоянные расходы. Меняйте под свои данные.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. «Юнит-экономика» — по каждой модели: закупка в юанях, розничная цена, доля в продажах. Итог — сколько остаётся с заказа и точка безубыточности (колонка «Средняя по долям»).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. «Прогноз» — введите план выкупленных заказов по месяцам и долю постоянных расходов на старте: увидите прибыль по месяцам, окупаемость и сколько денег нужно с учётом закупок товара.</t>
   </si>
   <si>
     <t xml:space="preserve">4. «Чувствительность» — сколько заказов в месяц нужно при другой цене и другой стоимости рекламы.</t>
   </si>
   <si>
+    <t xml:space="preserve">Главные понятия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Себестоимость в Ташкенте — сколько стоит одна сумка на нашем складе: закупка, байер, упаковка, доставка, пошлина, НДС, брокер.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Остаётся с заказа — цена минус себестоимость и все расходы на продажу (доставка, налог, комиссии, реклама). Из этих денег платятся постоянные расходы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точка безубыточности — сколько заказов в месяц нужно, чтобы покрыть постоянные расходы.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Обозначения</t>
   </si>
   <si>
-    <t xml:space="preserve">Синий текст на жёлтом фоне — ячейки для ввода. Синий текст без заливки — тоже ввод, но второстепенный.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чёрный текст — формулы, не трогайте. Зелёный — ссылка на лист «Допущения».</t>
+    <t xml:space="preserve">Синий текст на жёлтом фоне — ячейки для ввода. Синий текст без заливки — дополнительные настройки (названия месяцев, сдвиги цены на листе «Чувствительность»).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чёрный текст — формулы, не трогайте. Зелёный — ссылка на другой лист.</t>
   </si>
   <si>
     <t xml:space="preserve">Голубая заливка — ключевые итоги. Красный текст — убыток или предупреждение.</t>
@@ -87,12 +99,18 @@
     <t xml:space="preserve">• Ставку пошлины по коду 4202 — у таможенного брокера до оплаты фабрике (в расчёте 20%).</t>
   </si>
   <si>
+    <t xml:space="preserve">• Ставку налога с оборота для продаж через Telegram и Instagram — у бухгалтера (в расчёте 1%, возможно 4%).</t>
+  </si>
+  <si>
     <t xml:space="preserve">• Цену фабрики и упаковки — по ответам 3–5 фабрик на 1688 или Alibaba.</t>
   </si>
   <si>
     <t xml:space="preserve">• Стоимость рекламы на заказ — по первым 2–4 неделям продаж.</t>
   </si>
   <si>
+    <t xml:space="preserve">• Статьи, которых нет в бизнес-плане и которые стоят на нуле: брак, возвраты, расходы на перевод в Китай, соцналог и налоги с зарплаты. Поставьте свои оценки.</t>
+  </si>
+  <si>
     <t xml:space="preserve">• Комиссию Uzum для категории «сумки» — в кабинете продавца, если переключаете канал на Uzum Market.</t>
   </si>
   <si>
@@ -108,7 +126,7 @@
     <t xml:space="preserve">НДС при ввозе 12%: uz2b.uz/en/blog/customs-duties-import-taxes-uzbekistan-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Налог с оборота 1%: buxgalter.uz/publish/doc/text212712_nk-2026_izmeneniya_po_nalogu_s_oborota_dlya_ip_i_samozanyatyh</t>
+    <t xml:space="preserve">Налог с оборота: buxgalter.uz/publish/doc/text212712_nk-2026_izmeneniya_po_nalogu_s_oborota_dlya_ip_i_samozanyatyh</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссии и логистика Uzum: billz.io/blog/marketplace-uzbekistana-kakoy-vybrat</t>
@@ -117,7 +135,7 @@
     <t xml:space="preserve">Допущения: общие для всех моделей</t>
   </si>
   <si>
-    <t xml:space="preserve">Синие цифры на жёлтом фоне — вводите свои значения. Остальные листы пересчитаются сами.</t>
+    <t xml:space="preserve">Синие цифры на жёлтом фоне — вводите свои значения. Остальные листы пересчитаются сами; на листе «Прогноз» отдельно вводятся план заказов и доля расходов в первые месяцы.</t>
   </si>
   <si>
     <t xml:space="preserve">Параметр</t>
@@ -165,13 +183,22 @@
     <t xml:space="preserve">Допущение. Обычная ставка байера — несколько процентов от суммы заказа.</t>
   </si>
   <si>
+    <t xml:space="preserve">Банк и конвертация при оплате в Китай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% от закупки и упаковки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В бизнес-плане 0%. Обычно банк или платёжный агент берёт 2–4% (спред + SWIFT). Поставьте фактический процент после первой оплаты.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Упаковка: пыльник, коробка, карточка</t>
   </si>
   <si>
     <t xml:space="preserve">¥ за сумку</t>
   </si>
   <si>
-    <t xml:space="preserve">Допущение: заказ упаковки у той же фабрики.</t>
+    <t xml:space="preserve">Допущение: упаковку заказываем у той же фабрики.</t>
   </si>
   <si>
     <t xml:space="preserve">Доставка Китай → Ташкент</t>
@@ -195,7 +222,7 @@
     <t xml:space="preserve">Минимальная пошлина</t>
   </si>
   <si>
-    <t xml:space="preserve">Из той же нормы 2018 года (norma.uz). Если пошлина по % меньше — берётся минимум.</t>
+    <t xml:space="preserve">Из той же нормы 2018 года (norma.uz). Если пошлина по проценту меньше — берётся минимум.</t>
   </si>
   <si>
     <t xml:space="preserve">НДС при ввозе</t>
@@ -216,6 +243,15 @@
     <t xml:space="preserve">Допущение: расходы на оформление партии, разделённые на число сумок в ней.</t>
   </si>
   <si>
+    <t xml:space="preserve">Брак и непродаваемый товар</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% партии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В бизнес-плане 0%. Обычно 1–3%; снижается проверкой у байера перед отгрузкой. Брак повышает себестоимость проданных сумок.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Продажа</t>
   </si>
   <si>
@@ -228,7 +264,7 @@
     <t xml:space="preserve">выбор из списка</t>
   </si>
   <si>
-    <t xml:space="preserve">«Свой магазин» — Telegram и Instagram с курьером. «Uzum Market» — комиссия и логистика маркетплейса.</t>
+    <t xml:space="preserve">«Свой магазин» — Telegram и Instagram с курьером. «Uzum Market» — комиссия, логистика и продвижение маркетплейса вместо курьера, эквайринга и своей рекламы.</t>
   </si>
   <si>
     <t xml:space="preserve">Средняя скидка от цены</t>
@@ -252,10 +288,16 @@
     <t xml:space="preserve">Доля отказов при осмотре</t>
   </si>
   <si>
-    <t xml:space="preserve">% заказов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Допущение. Отказ = ещё одна поездка курьера впустую; сумка возвращается на склад.</t>
+    <t xml:space="preserve">% от выкупленных заказов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допущение. Отказ у двери = лишняя поездка курьера; сумка возвращается на склад.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Возвраты после покупки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В бизнес-плане 0%. Возврат = две поездки курьера, сумка возвращается на склад. Поставьте свою оценку, например 2–3%.</t>
   </si>
   <si>
     <t xml:space="preserve">Налог с оборота (ИП)</t>
@@ -264,19 +306,19 @@
     <t xml:space="preserve">% от выручки</t>
   </si>
   <si>
-    <t xml:space="preserve">1% при обороте до 1 млрд сум в год (buxgalter.uz, НК 2026). Выше — НДС и налог на прибыль.</t>
+    <t xml:space="preserve">1% для ИП с оборотом до 1 млрд сум в год (buxgalter.uz, НК-2026). В том же обзоре для электронной торговли указана ставка 4% — до запуска уточните у бухгалтера, какая применяется к продажам через Telegram и Instagram. При 4% точка безубыточности — около 148 заказов в месяц.</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссия за оплату (Click, Payme)</t>
   </si>
   <si>
-    <t xml:space="preserve">Допущение. Для Uzum не применяется: оплата внутри маркетплейса.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реклама на один заказ (CAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Допущение: таргет, блогеры, посевы в Telegram. Считайте фактическую по неделям.</t>
+    <t xml:space="preserve">Допущение. Для Uzum не применяется: оплата проходит внутри маркетплейса.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реклама на один выкупленный заказ (CAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допущение: таргет, блогеры, посевы в Telegram. Рекламный бюджет / число выкупленных заказов (без отказов). Если делите на все заявки — разделите результат на (1 − доля отказов).</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссия Uzum Market</t>
@@ -291,6 +333,12 @@
     <t xml:space="preserve">Около 8 000 сум за единицу (billz.io); зависит от размера товара.</t>
   </si>
   <si>
+    <t xml:space="preserve">Продвижение внутри Uzum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допущение: реклама в кабинете Uzum вместо своего таргета и блогеров. Уточните по первым неделям.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Постоянные расходы в месяц (полная загрузка)</t>
   </si>
   <si>
@@ -306,7 +354,7 @@
     <t xml:space="preserve">Менеджер заказов</t>
   </si>
   <si>
-    <t xml:space="preserve">Telegram, подтверждение заказов, курьеры.</t>
+    <t xml:space="preserve">Telegram, подтверждение заказов, курьеры. При продаже только через Uzum может быть не нужен.</t>
   </si>
   <si>
     <t xml:space="preserve">Хранение товара</t>
@@ -321,6 +369,12 @@
     <t xml:space="preserve">Бухгалтер на аутсорсе</t>
   </si>
   <si>
+    <t xml:space="preserve">Соцналог ИП и налоги с зарплаты менеджера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В бизнес-плане 0. ИП платит соцналог за себя (не меньше 1 БРВ в месяц), за оформленного менеджера — НДФЛ и соцналог. Сумму уточните у бухгалтера; ориентир — около 1,1 млн сум.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Прочее</t>
   </si>
   <si>
@@ -336,7 +390,7 @@
     <t xml:space="preserve">Юнит-экономика: сколько остаётся с одной сумки</t>
   </si>
   <si>
-    <t xml:space="preserve">Суммы в сумах на одну сумку (один заказ). Синие ячейки — ввод, чёрные — формулы, зелёные — ссылки на «Допущения».</t>
+    <t xml:space="preserve">Суммы в сумах на одну сумку (один выкупленный заказ). Синие ячейки — ввод, чёрные — формулы, зелёные — ссылки на другие листы.</t>
   </si>
   <si>
     <t xml:space="preserve">Показатель</t>
@@ -375,7 +429,7 @@
     <t xml:space="preserve">¥</t>
   </si>
   <si>
-    <t xml:space="preserve">Цена фабрики за 1 шт. без доставки. Пример — из бизнес-плана.</t>
+    <t xml:space="preserve">Цена фабрики за 1 шт. без доставки. Цифры — из бизнес-плана.</t>
   </si>
   <si>
     <t xml:space="preserve">Розничная цена</t>
@@ -399,10 +453,10 @@
     <t xml:space="preserve">¥ × курс юаня</t>
   </si>
   <si>
-    <t xml:space="preserve">Байер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">закупка × комиссия байера</t>
+    <t xml:space="preserve">Байер и оплата в Китай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">закупка × комиссия байера + (закупка + упаковка) × расходы на перевод</t>
   </si>
   <si>
     <t xml:space="preserve">¥ упаковки × курс юаня</t>
@@ -432,7 +486,7 @@
     <t xml:space="preserve">Себестоимость сумки в Ташкенте</t>
   </si>
   <si>
-    <t xml:space="preserve">сумма строк выше, кроме справочной</t>
+    <t xml:space="preserve">сумма строк выше, кроме справочной; с учётом брака: делим на (1 − доля брака)</t>
   </si>
   <si>
     <t xml:space="preserve">Продажа одного заказа</t>
@@ -450,10 +504,10 @@
     <t xml:space="preserve">свой магазин — курьер; Uzum — логистика маркетплейса</t>
   </si>
   <si>
-    <t xml:space="preserve">Отказы при осмотре</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доставка × доля отказов: лишние поездки на каждый заказ</t>
+    <t xml:space="preserve">Отказы и возвраты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лишние поездки курьера: отказ у двери — одна, возврат после покупки — две</t>
   </si>
   <si>
     <t xml:space="preserve">Налог с оборота</t>
@@ -477,6 +531,9 @@
     <t xml:space="preserve">Реклама на один заказ</t>
   </si>
   <si>
+    <t xml:space="preserve">свой магазин — CAC из «Допущений»; Uzum — % продвижения внутри Uzum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Расходы на продажу</t>
   </si>
   <si>
@@ -492,19 +549,19 @@
     <t xml:space="preserve">цена после скидки − себестоимость − расходы на продажу; до постоянных расходов</t>
   </si>
   <si>
-    <t xml:space="preserve">Доля от цены</t>
+    <t xml:space="preserve">Остаётся с заказа, % от цены</t>
   </si>
   <si>
     <t xml:space="preserve">остаётся с заказа / цена после скидки</t>
   </si>
   <si>
-    <t xml:space="preserve">Наценка: цена / себестоимость</t>
+    <t xml:space="preserve">Цена ÷ себестоимость (во сколько раз)</t>
   </si>
   <si>
     <t xml:space="preserve">раз</t>
   </si>
   <si>
-    <t xml:space="preserve">в моде обычно нужна наценка от 2 раз, чтобы покрыть продажу и рекламу</t>
+    <t xml:space="preserve">в моде обычно нужна цена не меньше двух себестоимостей, чтобы покрыть продажу и рекламу</t>
   </si>
   <si>
     <t xml:space="preserve">Предельная реклама на заказ</t>
@@ -519,7 +576,7 @@
     <t xml:space="preserve">цена до скидки, при которой с заказа остаётся 0 (без постоянных расходов)</t>
   </si>
   <si>
-    <t xml:space="preserve">Безубыточность</t>
+    <t xml:space="preserve">Безубыточность (по колонке «Средняя по долям»)</t>
   </si>
   <si>
     <t xml:space="preserve">Постоянные расходы в месяц</t>
@@ -531,7 +588,7 @@
     <t xml:space="preserve">заказов в мес.</t>
   </si>
   <si>
-    <t xml:space="preserve">постоянные расходы / средний доход с заказа (колонка H)</t>
+    <t xml:space="preserve">постоянные расходы / «Остаётся с заказа» (колонка «Средняя по долям»). Чтобы выйти в плюс, нужен следующий целый заказ.</t>
   </si>
   <si>
     <t xml:space="preserve">То же в день</t>
@@ -543,13 +600,16 @@
     <t xml:space="preserve">при 30 днях в месяце</t>
   </si>
   <si>
-    <t xml:space="preserve">Прогноз на 12 месяцев: заказы → прибыль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вводите заказы и постоянные расходы по месяцам (синие ячейки). Доход с заказа берётся из колонки «Средняя» листа «Юнит-экономика».</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Показатель, сум</t>
+    <t xml:space="preserve">Предел для налога с оборота 1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выше — оборот больше 1 млрд сум в год: вместо налога 1% — НДС 12% и налог на прибыль, с заказа остаётся меньше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прогноз на 12 месяцев: заказы → прибыль → деньги</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вводите выкупленные заказы по месяцам и долю постоянных расходов (жёлтые ячейки). Постоянные расходы берутся из «Допущений»; цена, себестоимость и расходы на заказ — из колонки «Средняя по долям» листа «Юнит-экономика».</t>
   </si>
   <si>
     <t xml:space="preserve">янв 2027</t>
@@ -591,34 +651,40 @@
     <t xml:space="preserve">Итого за год</t>
   </si>
   <si>
-    <t xml:space="preserve">Заказов в месяц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Постоянные расходы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выручка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Себестоимость проданных сумок</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расходы на продажу (доставка, налог, реклама…)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Остаётся с заказов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Операционная прибыль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Накопленная операционная прибыль</t>
+    <t xml:space="preserve">Выкупленных заказов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянные расходы, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля от полной загрузки (постоянных расходов)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Себестоимость проданных сумок, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расходы на продажу (доставка, налог, реклама…), сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Остаётся с заказов, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Операционная прибыль, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накопленная операционная прибыль, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка с начала года, сум</t>
   </si>
   <si>
     <t xml:space="preserve">Месяцев с прибылью</t>
   </si>
   <si>
-    <t xml:space="preserve">Оборот за год против порога налога с оборота</t>
+    <t xml:space="preserve">Налог с оборота 1%: порог 1 млрд сум в год</t>
   </si>
   <si>
     <t xml:space="preserve">Стартовые вложения (до запуска)</t>
@@ -657,22 +723,58 @@
     <t xml:space="preserve">Всего до запуска</t>
   </si>
   <si>
-    <t xml:space="preserve">Результат с учётом вложений без товара</t>
-  </si>
-  <si>
-    <t xml:space="preserve">служебная строка: номер месяца, если результат ≥ 0</t>
+    <t xml:space="preserve">Накопленная прибыль минус вложения без товара, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">служебная строка: месяц, после которого результат не уходит в минус</t>
   </si>
   <si>
     <t xml:space="preserve">Окупаемость вложений без товара</t>
   </si>
   <si>
-    <t xml:space="preserve">Товар на складе не считаем расходом: это деньги, которые вернутся с продажами.</t>
+    <t xml:space="preserve">Товар на складе здесь не считается расходом. Но деньги в нём заморожены — сколько денег нужно на самом деле, смотрите ниже.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Деньги с учётом закупок товара</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запас на начало месяца, в месяцах продаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,3 — как в бизнес-плане. Товар оплачиваем за месяц до продажи; путь из Китая около 12 недель, поэтому для надёжности ставьте 2 и больше.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закупка, шт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Остаток на складе на конец месяца, шт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оплата товара, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денежный поток месяца, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Деньги нарастающим итогом, с вложениями до запуска, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сколько денег нужно: самый глубокий минус</t>
+  </si>
+  <si>
+    <t xml:space="preserve">То же с резервом 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Товар на складе на конец декабря, сум</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эти деньги вернутся с продажами следующего года</t>
   </si>
   <si>
     <t xml:space="preserve">Точка безубыточности: заказов в месяц</t>
   </si>
   <si>
-    <t xml:space="preserve">Как меняется нужное число заказов, если сдвинуть цену (столбцы) и стоимость рекламы на заказ (строки). Постоянные расходы — из «Допущений».</t>
+    <t xml:space="preserve">Сколько заказов в месяц нужно, если сдвинуть цену (столбцы) и стоимость рекламы на заказ (строки). Постоянные расходы — из «Допущений».</t>
   </si>
   <si>
     <t xml:space="preserve">Средняя цена после скидки</t>
@@ -681,7 +783,7 @@
     <t xml:space="preserve">Средняя себестоимость в Ташкенте</t>
   </si>
   <si>
-    <t xml:space="preserve">Доставка и отказы на заказ</t>
+    <t xml:space="preserve">Доставка, отказы и возвраты на заказ</t>
   </si>
   <si>
     <t xml:space="preserve">Налоги и комиссии, % от цены</t>
@@ -690,25 +792,34 @@
     <t xml:space="preserve">Реклама на заказ, сум ↓ / цена →</t>
   </si>
   <si>
-    <t xml:space="preserve">Столбец «0%» и строка с текущей рекламой из «Допущений» — базовый расчёт. Зелёное — меньше заказов нужно, красное — больше.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цифры в заголовках (сдвиг цены и реклама) можно менять.</t>
+    <t xml:space="preserve">Ячейка в жирной рамке (цена 0%, реклама из «Юнит-экономики») — базовый расчёт. Зелёное — нужно меньше заказов, красное — больше.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сдвиги цены в строке 10 можно менять. Шкала рекламы строится вокруг текущей рекламы с шагом 10 000 сум.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Серым курсивом — оборот выше 1 млрд сум в год: налог 1% уже не действует, реальная точка безубыточности выше.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Для Uzum Market реклама в шкале — в сумах на заказ при текущей цене.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\–"/>
-    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\–"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;\(#,##0.0\);\–"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;\(#,##0.00\);\–"/>
-    <numFmt numFmtId="169" formatCode="0.00\x"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="\+0%;\-0%;0%"/>
+    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\–"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="\+0%;\-0%;0%"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -803,14 +914,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -838,6 +941,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -930,7 +1041,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -967,66 +1078,70 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1035,19 +1150,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1055,27 +1166,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1083,6 +1210,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1095,16 +1226,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1116,7 +1255,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1148,6 +1287,30 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+      </font>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="medium"/>
+        <right style="medium"/>
+        <top style="medium"/>
+        <bottom style="medium"/>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <i val="1"/>
+        <color rgb="FF7F7F7F"/>
+      </font>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1162,7 +1325,7 @@
       <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
@@ -1393,7 +1556,7 @@
     <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1415,17 +1578,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1443,13 +1606,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1467,7 +1629,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5"/>
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
@@ -1483,15 +1646,15 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4"/>
-    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1510,7 +1673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
@@ -1518,6 +1681,39 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1537,42 +1733,42 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1580,35 +1776,35 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>11800</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>1650</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1616,342 +1812,412 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <v>0.05</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>14</v>
+        <v>45</v>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="14" t="n">
         <v>3.4</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="13" t="n">
+      <c r="C13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>0.12</v>
+        <v>57</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>1.5</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="12" t="s">
         <v>52</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>60</v>
+      <c r="C17" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>0.08</v>
+        <v>73</v>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>0.01</v>
+        <v>76</v>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>30000</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>0.2</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>78</v>
+        <v>85</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>8000</v>
+        <v>87</v>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>0.01</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="A29" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="17" t="n">
-        <v>8000000</v>
+        <v>93</v>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>8000</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>84</v>
+        <v>77</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="17" t="n">
-        <v>5000000</v>
+        <v>95</v>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>0.05</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="17" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>88</v>
+        <v>74</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="17" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="12"/>
+      <c r="A33" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="17" t="n">
-        <v>1000000</v>
+        <v>98</v>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>8000000</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="12"/>
+        <v>99</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="10" t="n">
         <v>1000000</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="19" t="n">
-        <f aca="false">SUM(B30:B35)</f>
+      <c r="C38" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="18" t="n">
+        <f aca="false">SUM(B34:B40)</f>
         <v>17000000</v>
       </c>
-      <c r="C36" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>94</v>
+      <c r="C41" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B19" type="list">
+    <dataValidation allowBlank="false" error="Выберите из списка: «Свой магазин» или «Uzum Market»" errorStyle="stop" errorTitle="Канал продаж" operator="between" prompt="Выберите из списка" promptTitle="Канал продаж" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21" type="list">
       <formula1>"Свой магазин,Uzum Market"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1972,64 +2238,64 @@
     <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="str">
-        <f aca="false">"Канал продаж: "&amp;Допущения!$B$19</f>
+      <c r="A3" s="19" t="str">
+        <f aca="false">IF(OR(Допущения!$B$21="Свой магазин",Допущения!$B$21="Uzum Market"),"Канал продаж: "&amp;Допущения!$B$21,"Канал продаж не распознан — расчёт идёт как для «Свой магазин». Выберите значение из списка: лист «Допущения», ячейка B21")</f>
         <v>Канал продаж: Свой магазин</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>105</v>
+      <c r="A4" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2041,41 +2307,41 @@
       <c r="I5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="14" t="n">
+      <c r="A6" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>95</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="13" t="n">
         <v>125</v>
       </c>
       <c r="H6" s="23" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C6:G6)</f>
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C6:G6)/$H$8)</f>
         <v>95.25</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>109</v>
+      <c r="I6" s="24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>111</v>
+      <c r="A7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>449000</v>
@@ -2092,48 +2358,48 @@
       <c r="G7" s="10" t="n">
         <v>649000</v>
       </c>
-      <c r="H7" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C7:G7)</f>
+      <c r="H7" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C7:G7)/$H$8)</f>
         <v>559000</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>112</v>
+      <c r="I7" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="A8" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="26" t="n">
         <f aca="false">SUM(C8:G8)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="26" t="str">
-        <f aca="false">IF(ABS(H8-1)&gt;0.001,"Внимание: доли должны давать 100%, сейчас "&amp;TEXT(H8,"0%"),"Доли в сумме 100% — всё верно")</f>
+      <c r="I8" s="16" t="str">
+        <f aca="false">IF(H8=0,"Задайте доли продаж моделей",IF(ABS(H8-1)&gt;0.001,"Доли в сумме "&amp;TEXT(H8,"0%")&amp;" — средняя считается пропорционально долям; проверьте ввод","Доли в сумме 100% — всё верно"))</f>
         <v>Доли в сумме 100% — всё верно</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2146,10 +2412,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>111</v>
+        <v>133</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C10" s="27" t="n">
         <f aca="false">C6*Допущения!$B$7</f>
@@ -2171,297 +2437,297 @@
         <f aca="false">G6*Допущения!$B$7</f>
         <v>206250</v>
       </c>
-      <c r="H10" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C10:G10)</f>
+      <c r="H10" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C10:G10)/$H$8)</f>
         <v>157162.5</v>
       </c>
-      <c r="I10" s="28" t="s">
-        <v>116</v>
+      <c r="I10" s="24" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>111</v>
+        <v>135</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C11" s="27" t="n">
-        <f aca="false">C10*Допущения!$B$10</f>
+        <f aca="false">C10*Допущения!$B$10+(C10+C12)*Допущения!$B$11</f>
         <v>5362.5</v>
       </c>
       <c r="D11" s="27" t="n">
-        <f aca="false">D10*Допущения!$B$10</f>
+        <f aca="false">D10*Допущения!$B$10+(D10+D12)*Допущения!$B$11</f>
         <v>7837.5</v>
       </c>
       <c r="E11" s="27" t="n">
-        <f aca="false">E10*Допущения!$B$10</f>
+        <f aca="false">E10*Допущения!$B$10+(E10+E12)*Допущения!$B$11</f>
         <v>7425</v>
       </c>
       <c r="F11" s="27" t="n">
-        <f aca="false">F10*Допущения!$B$10</f>
+        <f aca="false">F10*Допущения!$B$10+(F10+F12)*Допущения!$B$11</f>
         <v>8250</v>
       </c>
       <c r="G11" s="27" t="n">
-        <f aca="false">G10*Допущения!$B$10</f>
+        <f aca="false">G10*Допущения!$B$10+(G10+G12)*Допущения!$B$11</f>
         <v>10312.5</v>
       </c>
-      <c r="H11" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C11:G11)</f>
+      <c r="H11" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C11:G11)/$H$8)</f>
         <v>7858.125</v>
       </c>
-      <c r="I11" s="28" t="s">
-        <v>118</v>
+      <c r="I11" s="24" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>111</v>
+        <v>48</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C12" s="27" t="n">
-        <f aca="false">Допущения!$B$11*Допущения!$B$7</f>
+        <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
       <c r="D12" s="27" t="n">
-        <f aca="false">Допущения!$B$11*Допущения!$B$7</f>
+        <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
       <c r="E12" s="27" t="n">
-        <f aca="false">Допущения!$B$11*Допущения!$B$7</f>
+        <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
       <c r="F12" s="27" t="n">
-        <f aca="false">Допущения!$B$11*Допущения!$B$7</f>
+        <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
       <c r="G12" s="27" t="n">
-        <f aca="false">Допущения!$B$11*Допущения!$B$7</f>
+        <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
-      <c r="H12" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C12:G12)</f>
+      <c r="H12" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C12:G12)/$H$8)</f>
         <v>23100</v>
       </c>
-      <c r="I12" s="28" t="s">
-        <v>119</v>
+      <c r="I12" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>111</v>
+        <v>51</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C13" s="27" t="n">
-        <f aca="false">Допущения!$B$12*Допущения!$B$6</f>
+        <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
       <c r="D13" s="27" t="n">
-        <f aca="false">Допущения!$B$12*Допущения!$B$6</f>
+        <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
       <c r="E13" s="27" t="n">
-        <f aca="false">Допущения!$B$12*Допущения!$B$6</f>
+        <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
       <c r="F13" s="27" t="n">
-        <f aca="false">Допущения!$B$12*Допущения!$B$6</f>
+        <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
       <c r="G13" s="27" t="n">
-        <f aca="false">Допущения!$B$12*Допущения!$B$6</f>
+        <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
-      <c r="H13" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C13:G13)</f>
+      <c r="H13" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C13:G13)/$H$8)</f>
         <v>40120</v>
       </c>
-      <c r="I13" s="28" t="s">
-        <v>120</v>
+      <c r="I13" s="24" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29" t="s">
-        <v>121</v>
+      <c r="A14" s="28" t="s">
+        <v>139</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="30" t="n">
+        <v>129</v>
+      </c>
+      <c r="C14" s="29" t="n">
         <f aca="false">C10+C12+C13</f>
         <v>170470</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="29" t="n">
         <f aca="false">D10+D12+D13</f>
         <v>219970</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="29" t="n">
         <f aca="false">E10+E12+E13</f>
         <v>211720</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="29" t="n">
         <f aca="false">F10+F12+F13</f>
         <v>228220</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="29" t="n">
         <f aca="false">G10+G12+G13</f>
         <v>269470</v>
       </c>
-      <c r="H14" s="31" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C14:G14)</f>
+      <c r="H14" s="30" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C14:G14)/$H$8)</f>
         <v>220382.5</v>
       </c>
-      <c r="I14" s="28" t="s">
-        <v>122</v>
+      <c r="I14" s="24" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C15" s="27" t="n">
-        <f aca="false">MAX(C14*Допущения!$B$13,Допущения!$B$14*Допущения!$B$6)</f>
+        <f aca="false">MAX(C14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>34094</v>
       </c>
       <c r="D15" s="27" t="n">
-        <f aca="false">MAX(D14*Допущения!$B$13,Допущения!$B$14*Допущения!$B$6)</f>
+        <f aca="false">MAX(D14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>43994</v>
       </c>
       <c r="E15" s="27" t="n">
-        <f aca="false">MAX(E14*Допущения!$B$13,Допущения!$B$14*Допущения!$B$6)</f>
+        <f aca="false">MAX(E14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>42344</v>
       </c>
       <c r="F15" s="27" t="n">
-        <f aca="false">MAX(F14*Допущения!$B$13,Допущения!$B$14*Допущения!$B$6)</f>
+        <f aca="false">MAX(F14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>45644</v>
       </c>
       <c r="G15" s="27" t="n">
-        <f aca="false">MAX(G14*Допущения!$B$13,Допущения!$B$14*Допущения!$B$6)</f>
+        <f aca="false">MAX(G14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>53894</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C15:G15)</f>
+      <c r="H15" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C15:G15)/$H$8)</f>
         <v>44076.5</v>
       </c>
-      <c r="I15" s="28" t="s">
-        <v>124</v>
+      <c r="I15" s="24" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>111</v>
+        <v>59</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C16" s="27" t="n">
-        <f aca="false">(C14+C15)*Допущения!$B$15</f>
+        <f aca="false">(C14+C15)*Допущения!$B$16</f>
         <v>24547.68</v>
       </c>
       <c r="D16" s="27" t="n">
-        <f aca="false">(D14+D15)*Допущения!$B$15</f>
+        <f aca="false">(D14+D15)*Допущения!$B$16</f>
         <v>31675.68</v>
       </c>
       <c r="E16" s="27" t="n">
-        <f aca="false">(E14+E15)*Допущения!$B$15</f>
+        <f aca="false">(E14+E15)*Допущения!$B$16</f>
         <v>30487.68</v>
       </c>
       <c r="F16" s="27" t="n">
-        <f aca="false">(F14+F15)*Допущения!$B$15</f>
+        <f aca="false">(F14+F15)*Допущения!$B$16</f>
         <v>32863.68</v>
       </c>
       <c r="G16" s="27" t="n">
-        <f aca="false">(G14+G15)*Допущения!$B$15</f>
+        <f aca="false">(G14+G15)*Допущения!$B$16</f>
         <v>38803.68</v>
       </c>
-      <c r="H16" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C16:G16)</f>
+      <c r="H16" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C16:G16)/$H$8)</f>
         <v>31735.08</v>
       </c>
-      <c r="I16" s="28" t="s">
-        <v>125</v>
+      <c r="I16" s="24" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="32" t="n">
-        <f aca="false">Допущения!$B$16</f>
+        <v>62</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="D17" s="32" t="n">
-        <f aca="false">Допущения!$B$16</f>
+      <c r="D17" s="27" t="n">
+        <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="E17" s="32" t="n">
-        <f aca="false">Допущения!$B$16</f>
+      <c r="E17" s="27" t="n">
+        <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="F17" s="32" t="n">
-        <f aca="false">Допущения!$B$16</f>
+      <c r="F17" s="27" t="n">
+        <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="G17" s="32" t="n">
-        <f aca="false">Допущения!$B$16</f>
+      <c r="G17" s="27" t="n">
+        <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="H17" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C17:G17)</f>
+      <c r="H17" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C17:G17)/$H$8)</f>
         <v>10000</v>
       </c>
-      <c r="I17" s="28" t="s">
-        <v>126</v>
+      <c r="I17" s="24" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="19" t="n">
-        <f aca="false">C10+C11+C12+C13+C15+C16+C17</f>
+      <c r="A18" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <f aca="false">(C10+C11+C12+C13+C15+C16+C17)/(1-Допущения!$B$18)</f>
         <v>244474.18</v>
       </c>
-      <c r="D18" s="19" t="n">
-        <f aca="false">D10+D11+D12+D13+D15+D16+D17</f>
+      <c r="D18" s="18" t="n">
+        <f aca="false">(D10+D11+D12+D13+D15+D16+D17)/(1-Допущения!$B$18)</f>
         <v>313477.18</v>
       </c>
-      <c r="E18" s="19" t="n">
-        <f aca="false">E10+E11+E12+E13+E15+E16+E17</f>
+      <c r="E18" s="18" t="n">
+        <f aca="false">(E10+E11+E12+E13+E15+E16+E17)/(1-Допущения!$B$18)</f>
         <v>301976.68</v>
       </c>
-      <c r="F18" s="19" t="n">
-        <f aca="false">F10+F11+F12+F13+F15+F16+F17</f>
+      <c r="F18" s="18" t="n">
+        <f aca="false">(F10+F11+F12+F13+F15+F16+F17)/(1-Допущения!$B$18)</f>
         <v>324977.68</v>
       </c>
-      <c r="G18" s="19" t="n">
-        <f aca="false">G10+G11+G12+G13+G15+G16+G17</f>
+      <c r="G18" s="18" t="n">
+        <f aca="false">(G10+G11+G12+G13+G15+G16+G17)/(1-Допущения!$B$18)</f>
         <v>382480.18</v>
       </c>
-      <c r="H18" s="19" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C18:G18)</f>
+      <c r="H18" s="18" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C18:G18)/$H$8)</f>
         <v>314052.205</v>
       </c>
-      <c r="I18" s="28" t="s">
-        <v>128</v>
+      <c r="I18" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2474,287 +2740,287 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>111</v>
+        <v>148</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C20" s="27" t="n">
-        <f aca="false">C7*(1-Допущения!$B$20)</f>
+        <f aca="false">C7*(1-Допущения!$B$22)</f>
         <v>449000</v>
       </c>
       <c r="D20" s="27" t="n">
-        <f aca="false">D7*(1-Допущения!$B$20)</f>
+        <f aca="false">D7*(1-Допущения!$B$22)</f>
         <v>549000</v>
       </c>
       <c r="E20" s="27" t="n">
-        <f aca="false">E7*(1-Допущения!$B$20)</f>
+        <f aca="false">E7*(1-Допущения!$B$22)</f>
         <v>549000</v>
       </c>
       <c r="F20" s="27" t="n">
-        <f aca="false">F7*(1-Допущения!$B$20)</f>
+        <f aca="false">F7*(1-Допущения!$B$22)</f>
         <v>599000</v>
       </c>
       <c r="G20" s="27" t="n">
-        <f aca="false">G7*(1-Допущения!$B$20)</f>
+        <f aca="false">G7*(1-Допущения!$B$22)</f>
         <v>649000</v>
       </c>
-      <c r="H20" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C20:G20)</f>
+      <c r="H20" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C20:G20)/$H$8)</f>
         <v>559000</v>
       </c>
-      <c r="I20" s="28" t="s">
-        <v>131</v>
+      <c r="I20" s="24" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>111</v>
+        <v>150</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C21" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",Допущения!$B$27,Допущения!$B$21)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
       <c r="D21" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",Допущения!$B$27,Допущения!$B$21)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
       <c r="E21" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",Допущения!$B$27,Допущения!$B$21)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
       <c r="F21" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",Допущения!$B$27,Допущения!$B$21)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
       <c r="G21" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",Допущения!$B$27,Допущения!$B$21)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
-      <c r="H21" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C21:G21)</f>
+      <c r="H21" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C21:G21)/$H$8)</f>
         <v>30000</v>
       </c>
-      <c r="I21" s="28" t="s">
-        <v>133</v>
+      <c r="I21" s="24" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>111</v>
+        <v>152</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C22" s="27" t="n">
-        <f aca="false">C21*Допущения!$B$22</f>
+        <f aca="false">C21*Допущения!$B$24+2*C21*Допущения!$B$25/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
       <c r="D22" s="27" t="n">
-        <f aca="false">D21*Допущения!$B$22</f>
+        <f aca="false">D21*Допущения!$B$24+2*D21*Допущения!$B$25/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
       <c r="E22" s="27" t="n">
-        <f aca="false">E21*Допущения!$B$22</f>
+        <f aca="false">E21*Допущения!$B$24+2*E21*Допущения!$B$25/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
       <c r="F22" s="27" t="n">
-        <f aca="false">F21*Допущения!$B$22</f>
+        <f aca="false">F21*Допущения!$B$24+2*F21*Допущения!$B$25/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
       <c r="G22" s="27" t="n">
-        <f aca="false">G21*Допущения!$B$22</f>
+        <f aca="false">G21*Допущения!$B$24+2*G21*Допущения!$B$25/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
-      <c r="H22" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C22:G22)</f>
+      <c r="H22" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C22:G22)/$H$8)</f>
         <v>2400</v>
       </c>
-      <c r="I22" s="28" t="s">
-        <v>135</v>
+      <c r="I22" s="24" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>111</v>
+        <v>154</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C23" s="27" t="n">
-        <f aca="false">C20*Допущения!$B$23</f>
+        <f aca="false">C20*Допущения!$B$26</f>
         <v>4490</v>
       </c>
       <c r="D23" s="27" t="n">
-        <f aca="false">D20*Допущения!$B$23</f>
+        <f aca="false">D20*Допущения!$B$26</f>
         <v>5490</v>
       </c>
       <c r="E23" s="27" t="n">
-        <f aca="false">E20*Допущения!$B$23</f>
+        <f aca="false">E20*Допущения!$B$26</f>
         <v>5490</v>
       </c>
       <c r="F23" s="27" t="n">
-        <f aca="false">F20*Допущения!$B$23</f>
+        <f aca="false">F20*Допущения!$B$26</f>
         <v>5990</v>
       </c>
       <c r="G23" s="27" t="n">
-        <f aca="false">G20*Допущения!$B$23</f>
+        <f aca="false">G20*Допущения!$B$26</f>
         <v>6490</v>
       </c>
-      <c r="H23" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C23:G23)</f>
+      <c r="H23" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C23:G23)/$H$8)</f>
         <v>5590</v>
       </c>
-      <c r="I23" s="28" t="s">
-        <v>137</v>
+      <c r="I23" s="24" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>111</v>
+        <v>156</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C24" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",0,C20*Допущения!$B$24)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",0,C20*Допущения!$B$27)</f>
         <v>4490</v>
       </c>
       <c r="D24" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",0,D20*Допущения!$B$24)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",0,D20*Допущения!$B$27)</f>
         <v>5490</v>
       </c>
       <c r="E24" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",0,E20*Допущения!$B$24)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",0,E20*Допущения!$B$27)</f>
         <v>5490</v>
       </c>
       <c r="F24" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",0,F20*Допущения!$B$24)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",0,F20*Допущения!$B$27)</f>
         <v>5990</v>
       </c>
       <c r="G24" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",0,G20*Допущения!$B$24)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",0,G20*Допущения!$B$27)</f>
         <v>6490</v>
       </c>
-      <c r="H24" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C24:G24)</f>
+      <c r="H24" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C24:G24)/$H$8)</f>
         <v>5590</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>139</v>
+      <c r="I24" s="24" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>111</v>
+        <v>158</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C25" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",C20*Допущения!$B$26,0)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",C20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
       <c r="D25" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",D20*Допущения!$B$26,0)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",D20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",E20*Допущения!$B$26,0)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",E20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
       <c r="F25" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",F20*Допущения!$B$26,0)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",F20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
       <c r="G25" s="27" t="n">
-        <f aca="false">IF(Допущения!$B$19="Uzum Market",G20*Допущения!$B$26,0)</f>
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",G20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C25:G25)</f>
+      <c r="H25" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C25:G25)/$H$8)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="28" t="s">
-        <v>141</v>
+      <c r="I25" s="24" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="32" t="n">
-        <f aca="false">Допущения!$B$25</f>
+        <v>160</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",C20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="D26" s="32" t="n">
-        <f aca="false">Допущения!$B$25</f>
+      <c r="D26" s="27" t="n">
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",D20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="E26" s="32" t="n">
-        <f aca="false">Допущения!$B$25</f>
+      <c r="E26" s="27" t="n">
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",E20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="F26" s="32" t="n">
-        <f aca="false">Допущения!$B$25</f>
+      <c r="F26" s="27" t="n">
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",F20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="G26" s="32" t="n">
-        <f aca="false">Допущения!$B$25</f>
+      <c r="G26" s="27" t="n">
+        <f aca="false">IF(Допущения!$B$21="Uzum Market",G20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="H26" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C26:G26)</f>
+      <c r="H26" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C26:G26)/$H$8)</f>
         <v>70000</v>
       </c>
-      <c r="I26" s="28" t="s">
-        <v>126</v>
+      <c r="I26" s="24" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="19" t="n">
+      <c r="A27" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="18" t="n">
         <f aca="false">SUM(C21:C26)</f>
         <v>111380</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">SUM(D21:D26)</f>
         <v>113380</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="18" t="n">
         <f aca="false">SUM(E21:E26)</f>
         <v>113380</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="18" t="n">
         <f aca="false">SUM(F21:F26)</f>
         <v>114380</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="18" t="n">
         <f aca="false">SUM(G21:G26)</f>
         <v>115380</v>
       </c>
-      <c r="H27" s="19" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C27:G27)</f>
+      <c r="H27" s="18" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C27:G27)/$H$8)</f>
         <v>113580</v>
       </c>
-      <c r="I27" s="28" t="s">
-        <v>144</v>
+      <c r="I27" s="24" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -2765,82 +3031,82 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="19" t="n">
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="18" t="n">
         <f aca="false">C20-C18-C27</f>
         <v>93145.82</v>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="18" t="n">
         <f aca="false">D20-D18-D27</f>
         <v>122142.82</v>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E29" s="18" t="n">
         <f aca="false">E20-E18-E27</f>
         <v>133643.32</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="18" t="n">
         <f aca="false">F20-F18-F27</f>
         <v>159642.32</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G29" s="18" t="n">
         <f aca="false">G20-G18-G27</f>
         <v>151139.82</v>
       </c>
-      <c r="H29" s="19" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C29:G29)</f>
+      <c r="H29" s="18" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C29:G29)/$H$8)</f>
         <v>131367.795</v>
       </c>
-      <c r="I29" s="28" t="s">
-        <v>147</v>
+      <c r="I29" s="24" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="33" t="n">
+        <v>167</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="32" t="n">
         <f aca="false">IFERROR(C29/C20,0)</f>
         <v>0.207451714922049</v>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="32" t="n">
         <f aca="false">IFERROR(D29/D20,0)</f>
         <v>0.222482367941712</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="32" t="n">
         <f aca="false">IFERROR(E29/E20,0)</f>
         <v>0.243430455373406</v>
       </c>
-      <c r="F30" s="33" t="n">
+      <c r="F30" s="32" t="n">
         <f aca="false">IFERROR(F29/F20,0)</f>
         <v>0.266514724540902</v>
       </c>
-      <c r="G30" s="33" t="n">
+      <c r="G30" s="32" t="n">
         <f aca="false">IFERROR(G29/G20,0)</f>
         <v>0.232881078582435</v>
       </c>
-      <c r="H30" s="25" t="n">
+      <c r="H30" s="33" t="n">
         <f aca="false">IFERROR(H29/H20,0)</f>
         <v>0.235005</v>
       </c>
-      <c r="I30" s="28" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>151</v>
+        <v>169</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>170</v>
       </c>
       <c r="C31" s="34" t="n">
         <f aca="false">IFERROR(C20/C18,0)</f>
@@ -2866,16 +3132,16 @@
         <f aca="false">IFERROR(H20/H18,0)</f>
         <v>1.77995884474048</v>
       </c>
-      <c r="I31" s="28" t="s">
-        <v>152</v>
+      <c r="I31" s="24" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>111</v>
+        <v>172</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C32" s="27" t="n">
         <f aca="false">C29+C26</f>
@@ -2897,52 +3163,52 @@
         <f aca="false">G29+G26</f>
         <v>221139.82</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C32:G32)</f>
+      <c r="H32" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C32:G32)/$H$8)</f>
         <v>201367.795</v>
       </c>
-      <c r="I32" s="28" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>111</v>
+        <v>174</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="C33" s="27" t="n">
-        <f aca="false">IFERROR((C18+C21+C22+C26)/(1-(C23+C24+C25)/C20)/(1-Допущения!$B$20),0)</f>
+        <f aca="false">IFERROR((C18+C21+C22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>353953.244897959</v>
       </c>
       <c r="D33" s="27" t="n">
-        <f aca="false">IFERROR((D18+D21+D22+D26)/(1-(D23+D24+D25)/D20)/(1-Допущения!$B$20),0)</f>
+        <f aca="false">IFERROR((D18+D21+D22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>424364.469387755</v>
       </c>
       <c r="E33" s="27" t="n">
-        <f aca="false">IFERROR((E18+E21+E22+E26)/(1-(E23+E24+E25)/E20)/(1-Допущения!$B$20),0)</f>
+        <f aca="false">IFERROR((E18+E21+E22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>412629.265306122</v>
       </c>
       <c r="F33" s="27" t="n">
-        <f aca="false">IFERROR((F18+F21+F22+F26)/(1-(F23+F24+F25)/F20)/(1-Допущения!$B$20),0)</f>
+        <f aca="false">IFERROR((F18+F21+F22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>436099.673469388</v>
       </c>
       <c r="G33" s="27" t="n">
-        <f aca="false">IFERROR((G18+G21+G22+G26)/(1-(G23+G24+G25)/G20)/(1-Допущения!$B$20),0)</f>
+        <f aca="false">IFERROR((G18+G21+G22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>494775.693877551</v>
       </c>
-      <c r="H33" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$8:$G$8,C33:G33)</f>
+      <c r="H33" s="25" t="n">
+        <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C33:G33)/$H$8)</f>
         <v>424951.229591837</v>
       </c>
-      <c r="I33" s="28" t="s">
-        <v>156</v>
+      <c r="I33" s="24" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -2954,53 +3220,78 @@
       <c r="I35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="32" t="n">
-        <f aca="false">Допущения!$B$36</f>
+      <c r="A36" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36" s="36" t="n">
+        <f aca="false">Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="19" t="n">
-        <f aca="false">IF(H29&lt;=0,"убыток с каждого заказа",C36/H29)</f>
+      <c r="I36" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H37" s="37" t="n">
+        <f aca="false">IF($H$8=0,"задайте доли",IF(ROUND(H29,0)&lt;=0,"убыток с заказа",H36/H29))</f>
         <v>129.407667990469</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>161</v>
+      <c r="I37" s="24" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" s="36" t="n">
-        <f aca="false">IF(ISNUMBER(C37),C37/30,"—")</f>
+      <c r="A38" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" s="38" t="n">
+        <f aca="false">IF(ISNUMBER(H37),H37/30,"—")</f>
         <v>4.31358893301564</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>164</v>
+      <c r="I38" s="24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H39" s="39" t="n">
+        <f aca="false">IF(H20&gt;0,1000000000/12/H20,"—")</f>
+        <v>149.075730471079</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ISNUMBER(SEARCH("не распознан",$A$3))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ABS($H$8-1)&gt;0.001</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C29:H29">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>C29&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3021,71 +3312,77 @@
     <tabColor rgb="FF70AD47"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="str">
+        <f aca="false">IF('Юнит-экономика'!$H$8=0,"Внимание: на листе «Юнит-экономика» не заданы доли продаж моделей (строка 8)","")</f>
+        <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="K4" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="N4" s="21" t="s">
-        <v>180</v>
+        <v>115</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="L4" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="M4" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>181</v>
+      <c r="A5" s="22" t="s">
+        <v>201</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>40</v>
@@ -3123,59 +3420,112 @@
       <c r="M5" s="10" t="n">
         <v>260</v>
       </c>
-      <c r="N5" s="24" t="n">
+      <c r="N5" s="25" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>1670</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <f aca="false">B7*Допущения!$B$41</f>
         <v>10000000</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="27" t="n">
+        <f aca="false">C7*Допущения!$B$41</f>
         <v>10000000</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="27" t="n">
+        <f aca="false">D7*Допущения!$B$41</f>
         <v>10000000</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="27" t="n">
+        <f aca="false">E7*Допущения!$B$41</f>
         <v>14000000</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="27" t="n">
+        <f aca="false">F7*Допущения!$B$41</f>
         <v>14000000</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="27" t="n">
+        <f aca="false">G7*Допущения!$B$41</f>
         <v>14000000</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="27" t="n">
+        <f aca="false">H7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="27" t="n">
+        <f aca="false">I7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="J6" s="27" t="n">
+        <f aca="false">J7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="27" t="n">
+        <f aca="false">K7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="L6" s="27" t="n">
+        <f aca="false">L7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="27" t="n">
+        <f aca="false">M7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="N6" s="24" t="n">
+      <c r="N6" s="25" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>174000000</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="42" t="n">
+        <v>0.588235294117647</v>
+      </c>
+      <c r="C7" s="42" t="n">
+        <v>0.588235294117647</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>0.588235294117647</v>
+      </c>
+      <c r="E7" s="42" t="n">
+        <v>0.823529411764706</v>
+      </c>
+      <c r="F7" s="42" t="n">
+        <v>0.823529411764706</v>
+      </c>
+      <c r="G7" s="42" t="n">
+        <v>0.823529411764706</v>
+      </c>
+      <c r="H7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>183</v>
+      <c r="A8" s="22" t="s">
+        <v>204</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">B5*'Юнит-экономика'!$H$20</f>
@@ -3225,14 +3575,14 @@
         <f aca="false">M5*'Юнит-экономика'!$H$20</f>
         <v>145340000</v>
       </c>
-      <c r="N8" s="24" t="n">
+      <c r="N8" s="25" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>933530000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>184</v>
+      <c r="A9" s="22" t="s">
+        <v>205</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">B5*'Юнит-экономика'!$H$18</f>
@@ -3282,14 +3632,14 @@
         <f aca="false">M5*'Юнит-экономика'!$H$18</f>
         <v>81653573.3</v>
       </c>
-      <c r="N9" s="24" t="n">
+      <c r="N9" s="25" t="n">
         <f aca="false">SUM(B9:M9)</f>
         <v>524467182.35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>185</v>
+      <c r="A10" s="22" t="s">
+        <v>206</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">B5*'Юнит-экономика'!$H$27</f>
@@ -3339,128 +3689,128 @@
         <f aca="false">M5*'Юнит-экономика'!$H$27</f>
         <v>29530800</v>
       </c>
-      <c r="N10" s="24" t="n">
+      <c r="N10" s="25" t="n">
         <f aca="false">SUM(B10:M10)</f>
         <v>189678600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="24" t="n">
+      <c r="A11" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <f aca="false">B8-B9-B10</f>
         <v>5254711.8</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <f aca="false">C8-C9-C10</f>
         <v>9195745.65</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="25" t="n">
         <f aca="false">D8-D9-D10</f>
         <v>19705169.25</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">E8-E9-E10</f>
         <v>13136779.5</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="25" t="n">
         <f aca="false">F8-F9-F10</f>
         <v>15764135.4</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="25" t="n">
         <f aca="false">G8-G9-G10</f>
         <v>17077813.35</v>
       </c>
-      <c r="H11" s="24" t="n">
+      <c r="H11" s="25" t="n">
         <f aca="false">H8-H9-H10</f>
         <v>15764135.4</v>
       </c>
-      <c r="I11" s="24" t="n">
+      <c r="I11" s="25" t="n">
         <f aca="false">I8-I9-I10</f>
         <v>18391491.3</v>
       </c>
-      <c r="J11" s="24" t="n">
+      <c r="J11" s="25" t="n">
         <f aca="false">J8-J9-J10</f>
         <v>21018847.2</v>
       </c>
-      <c r="K11" s="24" t="n">
+      <c r="K11" s="25" t="n">
         <f aca="false">K8-K9-K10</f>
         <v>23646203.1</v>
       </c>
-      <c r="L11" s="24" t="n">
+      <c r="L11" s="25" t="n">
         <f aca="false">L8-L9-L10</f>
         <v>26273559</v>
       </c>
-      <c r="M11" s="24" t="n">
+      <c r="M11" s="25" t="n">
         <f aca="false">M8-M9-M10</f>
         <v>34155626.7</v>
       </c>
-      <c r="N11" s="24" t="n">
+      <c r="N11" s="25" t="n">
         <f aca="false">SUM(B11:M11)</f>
         <v>219384217.65</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="18" t="n">
         <f aca="false">B11-B6</f>
         <v>-4745288.2</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="18" t="n">
         <f aca="false">C11-C6</f>
         <v>-804254.350000002</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">D11-D6</f>
         <v>9705169.25</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">E11-E6</f>
         <v>-863220.5</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <f aca="false">F11-F6</f>
         <v>1764135.4</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <f aca="false">G11-G6</f>
         <v>3077813.35</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="18" t="n">
         <f aca="false">H11-H6</f>
         <v>-1235864.6</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="18" t="n">
         <f aca="false">I11-I6</f>
         <v>1391491.3</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="18" t="n">
         <f aca="false">J11-J6</f>
         <v>4018847.2</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="18" t="n">
         <f aca="false">K11-K6</f>
         <v>6646203.09999999</v>
       </c>
-      <c r="L12" s="19" t="n">
+      <c r="L12" s="18" t="n">
         <f aca="false">L11-L6</f>
         <v>9273559</v>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="M12" s="18" t="n">
         <f aca="false">M11-M6</f>
         <v>17155626.7</v>
       </c>
-      <c r="N12" s="19" t="n">
+      <c r="N12" s="18" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>45384217.65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>188</v>
+      <c r="A13" s="22" t="s">
+        <v>209</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">B12</f>
@@ -3511,9 +3861,62 @@
         <v>45384217.65</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="27" t="n">
+        <f aca="false">B8</f>
+        <v>22360000</v>
+      </c>
+      <c r="C14" s="27" t="n">
+        <f aca="false">B14+C8</f>
+        <v>61490000</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <f aca="false">C14+D8</f>
+        <v>145340000</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <f aca="false">D14+E8</f>
+        <v>201240000</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <f aca="false">E14+F8</f>
+        <v>268320000</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <f aca="false">F14+G8</f>
+        <v>340990000</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <f aca="false">G14+H8</f>
+        <v>408070000</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <f aca="false">H14+I8</f>
+        <v>486330000</v>
+      </c>
+      <c r="J14" s="27" t="n">
+        <f aca="false">I14+J8</f>
+        <v>575770000</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <f aca="false">J14+K8</f>
+        <v>676390000</v>
+      </c>
+      <c r="L14" s="27" t="n">
+        <f aca="false">K14+L8</f>
+        <v>788190000</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <f aca="false">L14+M8</f>
+        <v>933530000</v>
+      </c>
+    </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>189</v>
+      <c r="A15" s="22" t="s">
+        <v>211</v>
       </c>
       <c r="B15" s="27" t="n">
         <f aca="false">COUNTIF(B12:M12,"&gt;0")</f>
@@ -3521,225 +3924,562 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="26" t="str">
-        <f aca="false">IF(N8&gt;1000000000,"Оборот выше 1 млрд сум — с месяца превышения ИП платит НДС и налог на прибыль","Оборот до 1 млрд сум — налог с оборота 1%")</f>
-        <v>Оборот до 1 млрд сум — налог с оборота 1%</v>
+      <c r="A16" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B16" s="17" t="str">
+        <f aca="false">IF(N8&gt;1000000000,"Оборот превысит 1 млрд сум в "&amp;INDEX(B4:M4,COUNTIF(B14:M14,"&lt;=1000000000")+1)&amp;": с этого месяца ИП платит НДС 12% и налог на прибыль — прибыль в строке 12 завышена","Оборот за год до 1 млрд сум — налог с оборота 1% сохраняется")</f>
+        <v>Оборот за год до 1 млрд сум — налог с оборота 1% сохраняется</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="8"/>
+        <v>129</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>192</v>
+      <c r="A19" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>6500000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>193</v>
+      <c r="A20" s="22" t="s">
+        <v>215</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>194</v>
+      <c r="A21" s="22" t="s">
+        <v>216</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>195</v>
+      <c r="A22" s="22" t="s">
+        <v>217</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>196</v>
+      <c r="A23" s="22" t="s">
+        <v>218</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>18000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>197</v>
+      <c r="A24" s="22" t="s">
+        <v>219</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="B25" s="24" t="n">
+      <c r="A25" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="25" t="n">
         <f aca="false">SUM(B19:B24)</f>
         <v>50500000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>199</v>
+      <c r="A26" s="22" t="s">
+        <v>221</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>200</v>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22" t="s">
+        <v>222</v>
       </c>
       <c r="B27" s="27" t="n">
         <f aca="false">B26*'Юнит-экономика'!$H$18</f>
         <v>62810441</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>201</v>
+      <c r="C27" s="24" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B28" s="19" t="n">
+      <c r="A28" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="18" t="n">
         <f aca="false">B25+B27</f>
         <v>113310441</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B30" s="24" t="n">
+      <c r="A30" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B30" s="25" t="n">
         <f aca="false">B13-$B$25</f>
         <v>-55245288.2</v>
       </c>
-      <c r="C30" s="24" t="n">
+      <c r="C30" s="25" t="n">
         <f aca="false">C13-$B$25</f>
         <v>-56049542.55</v>
       </c>
-      <c r="D30" s="24" t="n">
+      <c r="D30" s="25" t="n">
         <f aca="false">D13-$B$25</f>
         <v>-46344373.3</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="25" t="n">
         <f aca="false">E13-$B$25</f>
         <v>-47207593.8</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="25" t="n">
         <f aca="false">F13-$B$25</f>
         <v>-45443458.4</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G30" s="25" t="n">
         <f aca="false">G13-$B$25</f>
         <v>-42365645.05</v>
       </c>
-      <c r="H30" s="24" t="n">
+      <c r="H30" s="25" t="n">
         <f aca="false">H13-$B$25</f>
         <v>-43601509.65</v>
       </c>
-      <c r="I30" s="24" t="n">
+      <c r="I30" s="25" t="n">
         <f aca="false">I13-$B$25</f>
         <v>-42210018.35</v>
       </c>
-      <c r="J30" s="24" t="n">
+      <c r="J30" s="25" t="n">
         <f aca="false">J13-$B$25</f>
         <v>-38191171.15</v>
       </c>
-      <c r="K30" s="24" t="n">
+      <c r="K30" s="25" t="n">
         <f aca="false">K13-$B$25</f>
         <v>-31544968.05</v>
       </c>
-      <c r="L30" s="24" t="n">
+      <c r="L30" s="25" t="n">
         <f aca="false">L13-$B$25</f>
         <v>-22271409.05</v>
       </c>
-      <c r="M30" s="24" t="n">
+      <c r="M30" s="25" t="n">
         <f aca="false">M13-$B$25</f>
         <v>-5115782.35000002</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="B31" s="39" t="n">
-        <f aca="false">IF(B30&gt;=0,1,99)</f>
+    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="44" t="n">
+        <f aca="false">IF(MIN(B30:$M$30)&gt;=0,1,99)</f>
         <v>99</v>
       </c>
-      <c r="C31" s="39" t="n">
-        <f aca="false">IF(C30&gt;=0,2,99)</f>
+      <c r="C31" s="44" t="n">
+        <f aca="false">IF(MIN(C30:$M$30)&gt;=0,2,99)</f>
         <v>99</v>
       </c>
-      <c r="D31" s="39" t="n">
-        <f aca="false">IF(D30&gt;=0,3,99)</f>
+      <c r="D31" s="44" t="n">
+        <f aca="false">IF(MIN(D30:$M$30)&gt;=0,3,99)</f>
         <v>99</v>
       </c>
-      <c r="E31" s="39" t="n">
-        <f aca="false">IF(E30&gt;=0,4,99)</f>
+      <c r="E31" s="44" t="n">
+        <f aca="false">IF(MIN(E30:$M$30)&gt;=0,4,99)</f>
         <v>99</v>
       </c>
-      <c r="F31" s="39" t="n">
-        <f aca="false">IF(F30&gt;=0,5,99)</f>
+      <c r="F31" s="44" t="n">
+        <f aca="false">IF(MIN(F30:$M$30)&gt;=0,5,99)</f>
         <v>99</v>
       </c>
-      <c r="G31" s="39" t="n">
-        <f aca="false">IF(G30&gt;=0,6,99)</f>
+      <c r="G31" s="44" t="n">
+        <f aca="false">IF(MIN(G30:$M$30)&gt;=0,6,99)</f>
         <v>99</v>
       </c>
-      <c r="H31" s="39" t="n">
-        <f aca="false">IF(H30&gt;=0,7,99)</f>
+      <c r="H31" s="44" t="n">
+        <f aca="false">IF(MIN(H30:$M$30)&gt;=0,7,99)</f>
         <v>99</v>
       </c>
-      <c r="I31" s="39" t="n">
-        <f aca="false">IF(I30&gt;=0,8,99)</f>
+      <c r="I31" s="44" t="n">
+        <f aca="false">IF(MIN(I30:$M$30)&gt;=0,8,99)</f>
         <v>99</v>
       </c>
-      <c r="J31" s="39" t="n">
-        <f aca="false">IF(J30&gt;=0,9,99)</f>
+      <c r="J31" s="44" t="n">
+        <f aca="false">IF(MIN(J30:$M$30)&gt;=0,9,99)</f>
         <v>99</v>
       </c>
-      <c r="K31" s="39" t="n">
-        <f aca="false">IF(K30&gt;=0,10,99)</f>
+      <c r="K31" s="44" t="n">
+        <f aca="false">IF(MIN(K30:$M$30)&gt;=0,10,99)</f>
         <v>99</v>
       </c>
-      <c r="L31" s="39" t="n">
-        <f aca="false">IF(L30&gt;=0,11,99)</f>
+      <c r="L31" s="44" t="n">
+        <f aca="false">IF(MIN(L30:$M$30)&gt;=0,11,99)</f>
         <v>99</v>
       </c>
-      <c r="M31" s="39" t="n">
-        <f aca="false">IF(M30&gt;=0,12,99)</f>
+      <c r="M31" s="44" t="n">
+        <f aca="false">IF(MIN(M30:$M$30)&gt;=0,12,99)</f>
         <v>99</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B32" s="40" t="str">
-        <f aca="false">IF(MIN(B31:M31)=99,"позже 12 месяцев",INDEX(B4:M4,MIN(B31:M31)))</f>
+      <c r="A32" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="45" t="str">
+        <f aca="false">IF(MIN(B31:M31)=99,IF(M12&lt;=0,"не окупается: в декабре убыток","позже 12 месяцев"),INDEX(B4:M4,MIN(B31:M31)))</f>
         <v>позже 12 месяцев</v>
       </c>
-      <c r="C32" s="2" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" s="46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(C5*$B$36,0)-($B$26-B5))</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(D5*$B$36,0)-(B38-C5))</f>
+        <v>105</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(E5*$B$36,0)-(C38-D5))</f>
+        <v>85</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(F5*$B$36,0)-(D38-E5))</f>
+        <v>126</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(G5*$B$36,0)-(E38-F5))</f>
+        <v>133</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(H5*$B$36,0)-(F38-G5))</f>
+        <v>117</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(I5*$B$36,0)-(G38-H5))</f>
+        <v>146</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(J5*$B$36,0)-(H38-I5))</f>
+        <v>166</v>
+      </c>
+      <c r="J37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(K5*$B$36,0)-(I38-J5))</f>
+        <v>186</v>
+      </c>
+      <c r="K37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(L5*$B$36,0)-(J38-K5))</f>
         <v>206</v>
+      </c>
+      <c r="L37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(M5*$B$36,0)-(K38-L5))</f>
+        <v>278</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <f aca="false">MAX(0,ROUND(M5*$B$36,0)-(L38-M5))</f>
+        <v>260</v>
+      </c>
+      <c r="N37" s="25" t="n">
+        <f aca="false">SUM(B37:M37)</f>
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" s="27" t="n">
+        <f aca="false">$B$26-B5+B37</f>
+        <v>160</v>
+      </c>
+      <c r="C38" s="27" t="n">
+        <f aca="false">B38-C5+C37</f>
+        <v>195</v>
+      </c>
+      <c r="D38" s="27" t="n">
+        <f aca="false">C38-D5+D37</f>
+        <v>130</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <f aca="false">D38-E5+E37</f>
+        <v>156</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <f aca="false">E38-F5+F37</f>
+        <v>169</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <f aca="false">F38-G5+G37</f>
+        <v>156</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <f aca="false">G38-H5+H37</f>
+        <v>182</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <f aca="false">H38-I5+I37</f>
+        <v>208</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <f aca="false">I38-J5+J37</f>
+        <v>234</v>
+      </c>
+      <c r="K38" s="27" t="n">
+        <f aca="false">J38-K5+K37</f>
+        <v>260</v>
+      </c>
+      <c r="L38" s="27" t="n">
+        <f aca="false">K38-L5+L37</f>
+        <v>338</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <f aca="false">L38-M5+M37</f>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="27" t="n">
+        <f aca="false">B37*'Юнит-экономика'!$H$18</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="27" t="n">
+        <f aca="false">C37*'Юнит-экономика'!$H$18</f>
+        <v>32975481.525</v>
+      </c>
+      <c r="D39" s="27" t="n">
+        <f aca="false">D37*'Юнит-экономика'!$H$18</f>
+        <v>26694437.425</v>
+      </c>
+      <c r="E39" s="27" t="n">
+        <f aca="false">E37*'Юнит-экономика'!$H$18</f>
+        <v>39570577.83</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <f aca="false">F37*'Юнит-экономика'!$H$18</f>
+        <v>41768943.265</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <f aca="false">G37*'Юнит-экономика'!$H$18</f>
+        <v>36744107.985</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <f aca="false">H37*'Юнит-экономика'!$H$18</f>
+        <v>45851621.93</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <f aca="false">I37*'Юнит-экономика'!$H$18</f>
+        <v>52132666.03</v>
+      </c>
+      <c r="J39" s="27" t="n">
+        <f aca="false">J37*'Юнит-экономика'!$H$18</f>
+        <v>58413710.13</v>
+      </c>
+      <c r="K39" s="27" t="n">
+        <f aca="false">K37*'Юнит-экономика'!$H$18</f>
+        <v>64694754.23</v>
+      </c>
+      <c r="L39" s="27" t="n">
+        <f aca="false">L37*'Юнит-экономика'!$H$18</f>
+        <v>87306512.99</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <f aca="false">M37*'Юнит-экономика'!$H$18</f>
+        <v>81653573.3</v>
+      </c>
+      <c r="N39" s="25" t="n">
+        <f aca="false">SUM(B39:M39)</f>
+        <v>567806386.64</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="27" t="n">
+        <f aca="false">B8-B10-B6-B39</f>
+        <v>7816800</v>
+      </c>
+      <c r="C40" s="27" t="n">
+        <f aca="false">C8-C10-C6-C39</f>
+        <v>-11796081.525</v>
+      </c>
+      <c r="D40" s="27" t="n">
+        <f aca="false">D8-D10-D6-D39</f>
+        <v>30118562.575</v>
+      </c>
+      <c r="E40" s="27" t="n">
+        <f aca="false">E8-E10-E6-E39</f>
+        <v>-9028577.83000001</v>
+      </c>
+      <c r="F40" s="27" t="n">
+        <f aca="false">F8-F10-F6-F39</f>
+        <v>-2318543.265</v>
+      </c>
+      <c r="G40" s="27" t="n">
+        <f aca="false">G8-G10-G6-G39</f>
+        <v>7160492.015</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <f aca="false">H8-H10-H6-H39</f>
+        <v>-9401221.93</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <f aca="false">I8-I10-I6-I39</f>
+        <v>-6773866.03</v>
+      </c>
+      <c r="J40" s="27" t="n">
+        <f aca="false">J8-J10-J6-J39</f>
+        <v>-4146510.13</v>
+      </c>
+      <c r="K40" s="27" t="n">
+        <f aca="false">K8-K10-K6-K39</f>
+        <v>-1519154.23</v>
+      </c>
+      <c r="L40" s="27" t="n">
+        <f aca="false">L8-L10-L6-L39</f>
+        <v>-15222512.99</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <f aca="false">M8-M10-M6-M39</f>
+        <v>17155626.7</v>
+      </c>
+      <c r="N40" s="25" t="n">
+        <f aca="false">SUM(B40:M40)</f>
+        <v>2045013.35999998</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" s="25" t="n">
+        <f aca="false">-$B$28+B40</f>
+        <v>-105493641</v>
+      </c>
+      <c r="C41" s="25" t="n">
+        <f aca="false">B41+C40</f>
+        <v>-117289722.525</v>
+      </c>
+      <c r="D41" s="25" t="n">
+        <f aca="false">C41+D40</f>
+        <v>-87171159.95</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <f aca="false">D41+E40</f>
+        <v>-96199737.78</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <f aca="false">E41+F40</f>
+        <v>-98518281.045</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <f aca="false">F41+G40</f>
+        <v>-91357789.03</v>
+      </c>
+      <c r="H41" s="25" t="n">
+        <f aca="false">G41+H40</f>
+        <v>-100759010.96</v>
+      </c>
+      <c r="I41" s="25" t="n">
+        <f aca="false">H41+I40</f>
+        <v>-107532876.99</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <f aca="false">I41+J40</f>
+        <v>-111679387.12</v>
+      </c>
+      <c r="K41" s="25" t="n">
+        <f aca="false">J41+K40</f>
+        <v>-113198541.35</v>
+      </c>
+      <c r="L41" s="25" t="n">
+        <f aca="false">K41+L40</f>
+        <v>-128421054.34</v>
+      </c>
+      <c r="M41" s="25" t="n">
+        <f aca="false">L41+M40</f>
+        <v>-111265427.64</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B43" s="18" t="n">
+        <f aca="false">MAX($B$28,-MIN(B41:M41))</f>
+        <v>128421054.34</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B44" s="18" t="n">
+        <f aca="false">B43*1.1</f>
+        <v>141263159.774</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" s="27" t="n">
+        <f aca="false">M38*'Юнит-экономика'!$H$18</f>
+        <v>106149645.29</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3748,9 +4488,19 @@
       <formula>B12&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$N$8&gt;1000000000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B30:M30">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>B30&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:N41">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>B40&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3769,477 +4519,502 @@
     <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="str">
+        <f aca="false">IF('Юнит-экономика'!$H$8=0,"Внимание: на листе «Юнит-экономика» не заданы доли продаж моделей (строка 8)","")</f>
+        <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="32" t="n">
+      <c r="A4" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="36" t="n">
         <f aca="false">'Юнит-экономика'!$H$20</f>
         <v>559000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="32" t="n">
+      <c r="A5" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="36" t="n">
         <f aca="false">'Юнит-экономика'!$H$18</f>
         <v>314052.205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="32" t="n">
+      <c r="A6" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <f aca="false">'Юнит-экономика'!$H$21+'Юнит-экономика'!$H$22</f>
         <v>32400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="B7" s="41" t="n">
+      <c r="A7" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" s="47" t="n">
         <f aca="false">IFERROR(('Юнит-экономика'!$H$23+'Юнит-экономика'!$H$24+'Юнит-экономика'!$H$25)/'Юнит-экономика'!$H$20,0)</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="32" t="n">
-        <f aca="false">Допущения!$B$36</f>
+      <c r="A8" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="36" t="n">
+        <f aca="false">Допущения!$B$41</f>
         <v>17000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="42" t="n">
+        <v>247</v>
+      </c>
+      <c r="B10" s="48" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="48" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="48" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="48" t="n">
         <v>0.05</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="48" t="n">
         <v>0.1</v>
       </c>
-      <c r="I10" s="42" t="n">
+      <c r="I10" s="48" t="n">
         <v>0.15</v>
       </c>
-      <c r="J10" s="42" t="n">
+      <c r="J10" s="48" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="27" t="n">
+        <f aca="false">MAX(0,$A$14-30000)</f>
         <v>40000</v>
       </c>
-      <c r="B11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="B11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>328.161286253256</v>
       </c>
-      <c r="C11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="C11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>214.660572074213</v>
       </c>
-      <c r="D11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="D11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>159.495925324758</v>
       </c>
-      <c r="E11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="E11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>126.887644983596</v>
       </c>
-      <c r="F11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="F11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>105.349397629186</v>
       </c>
-      <c r="G11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="G11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>90.062028632891</v>
       </c>
-      <c r="H11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="H11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>78.6491608747536</v>
       </c>
-      <c r="I11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="I11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>69.8035004771993</v>
       </c>
-      <c r="J11" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="J11" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
         <v>62.7464192602422</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="27" t="n">
+        <f aca="false">MAX(0,$A$14-20000)</f>
         <v>50000</v>
       </c>
-      <c r="B12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="B12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>406.661643996676</v>
       </c>
-      <c r="C12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="C12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>245.68321938088</v>
       </c>
-      <c r="D12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="D12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>176.009318968695</v>
       </c>
-      <c r="E12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="E12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>137.122434887916</v>
       </c>
-      <c r="F12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="F12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>112.309226675331</v>
       </c>
-      <c r="G12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="G12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>95.1002159082578</v>
       </c>
-      <c r="H12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="H12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>82.4643070831092</v>
       </c>
-      <c r="I12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="I12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>72.7924215553004</v>
       </c>
-      <c r="J12" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="J12" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
         <v>65.1511250286689</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="n">
+      <c r="A13" s="27" t="n">
+        <f aca="false">MAX(0,$A$14-10000)</f>
         <v>60000</v>
       </c>
-      <c r="B13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="B13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>534.527404669789</v>
       </c>
-      <c r="C13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="C13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>287.18741233921</v>
       </c>
-      <c r="D13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="D13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>196.337055056202</v>
       </c>
-      <c r="E13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="E13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>149.153167537304</v>
       </c>
-      <c r="F13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="F13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>120.253697102653</v>
       </c>
-      <c r="G13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="G13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>100.735490556211</v>
       </c>
-      <c r="H13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="H13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>86.6684566252032</v>
       </c>
-      <c r="I13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="I13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>76.0487587959057</v>
       </c>
-      <c r="J13" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="J13" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
         <v>67.7474928994152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="n">
+      <c r="A14" s="50" t="n">
+        <f aca="false">'Юнит-экономика'!$H$26</f>
         <v>70000</v>
       </c>
-      <c r="B14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="B14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>779.680784927579</v>
       </c>
-      <c r="C14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="C14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>345.56501353446</v>
       </c>
-      <c r="D14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="D14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>221.973278465021</v>
       </c>
-      <c r="E14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="E14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>163.498018957018</v>
       </c>
-      <c r="F14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="F14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>129.407667990469</v>
       </c>
-      <c r="G14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="G14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>107.080681734829</v>
       </c>
-      <c r="H14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="H14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>91.3243014852635</v>
       </c>
-      <c r="I14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="I14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>79.6100810620285</v>
       </c>
-      <c r="J14" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="J14" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
         <v>70.5593879794902</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="27" t="n">
+        <f aca="false">$A$14+10000</f>
         <v>80000</v>
       </c>
-      <c r="B15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="B15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>1440.21477838272</v>
       </c>
-      <c r="C15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="C15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>433.731060463513</v>
       </c>
-      <c r="D15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="D15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>255.309709826248</v>
       </c>
-      <c r="E15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="E15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>180.895720055148</v>
       </c>
-      <c r="F15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="F15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>140.070106736305</v>
       </c>
-      <c r="G15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="G15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>114.278957422316</v>
       </c>
-      <c r="H15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="H15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>96.5087697093261</v>
       </c>
-      <c r="I15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="I15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>83.5213402797213</v>
       </c>
-      <c r="J15" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="J15" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
         <v>73.6148090824826</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="27" t="n">
+        <f aca="false">$A$14+20000</f>
         <v>90000</v>
       </c>
-      <c r="B16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="B16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>9424.57430029474</v>
       </c>
-      <c r="C16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="C16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>582.295577002682</v>
       </c>
-      <c r="D16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="D16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>300.428756015534</v>
       </c>
-      <c r="E16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="E16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>202.436875567828</v>
       </c>
-      <c r="F16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="F16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>152.647360935897</v>
       </c>
-      <c r="G16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="G16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>122.514756632183</v>
       </c>
-      <c r="H16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="H16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>102.317309509771</v>
       </c>
-      <c r="I16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="I16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>87.8367788041793</v>
       </c>
-      <c r="J16" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="J16" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
         <v>76.9468242450119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="27" t="n">
+        <f aca="false">$A$14+30000</f>
         <v>100000</v>
       </c>
-      <c r="B17" s="43" t="str">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="B17" s="49" t="str">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>убыток</v>
       </c>
-      <c r="C17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="C17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>885.656762679675</v>
       </c>
-      <c r="D17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="D17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>364.918104327725</v>
       </c>
-      <c r="E17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="E17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>229.801791223856</v>
       </c>
-      <c r="F17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="F17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>167.706124020948</v>
       </c>
-      <c r="G17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="G17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>132.029815905003</v>
       </c>
-      <c r="H17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="H17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>108.869819521697</v>
       </c>
-      <c r="I17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="I17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>92.6224603091645</v>
       </c>
-      <c r="J17" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="J17" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
         <v>80.5947723528357</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="27" t="n">
+        <f aca="false">$A$14+40000</f>
         <v>110000</v>
       </c>
-      <c r="B18" s="43" t="str">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="B18" s="49" t="str">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>убыток</v>
       </c>
-      <c r="C18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="C18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>1848.87210644718</v>
       </c>
-      <c r="D18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="D18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>464.661216190601</v>
       </c>
-      <c r="E18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="E18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>265.721344746951</v>
       </c>
-      <c r="F18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="F18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>186.061182717609</v>
       </c>
-      <c r="G18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="G18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>143.147292796294</v>
       </c>
-      <c r="H18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="H18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>116.319013653081</v>
       </c>
-      <c r="I18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="I18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>97.9596757062223</v>
       </c>
-      <c r="J18" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="J18" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
         <v>84.6058235830721</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="27" t="n">
+        <f aca="false">$A$14+50000</f>
         <v>120000</v>
       </c>
-      <c r="B19" s="43" t="str">
-        <f aca="false">IF(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="B19" s="49" t="str">
+        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>убыток</v>
       </c>
-      <c r="C19" s="43" t="str">
-        <f aca="false">IF(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="C19" s="49" t="str">
+        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>убыток</v>
       </c>
-      <c r="D19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="D19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>639.439219327465</v>
       </c>
-      <c r="E19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="E19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>314.950155895696</v>
       </c>
-      <c r="F19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="F19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>208.927868820828</v>
       </c>
-      <c r="G19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="G19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>156.30919779867</v>
       </c>
-      <c r="H19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="H19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>124.862472249775</v>
       </c>
-      <c r="I19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="I19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>103.949598630727</v>
       </c>
-      <c r="J19" s="43" t="n">
-        <f aca="false">IF(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="J19" s="49" t="n">
+        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
         <v>89.0370302128045</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>215</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4257,6 +5032,12 @@
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>B11="убыток"</formula>
     </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>AND(B$10=0,$A11=$A$14)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>AND(ISNUMBER(B11),B11*$B$4*(1+B$10)*12&gt;1000000000)</formula>
+    </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/sumki/Калькулятор_юнит-экономики_сумки.xlsx
+++ b/sumki/Калькулятор_юнит-экономики_сумки.xlsx
@@ -14,6 +14,11 @@
     <sheet name="Прогноз" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Чувствительность" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">Прогноз!$A:$A,Прогноз!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Юнит-экономика'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">Прогноз!$4:$4,Прогноз!$A:$A</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -46,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="251">
   <si>
     <t xml:space="preserve">Калькулятор юнит-экономики: онлайн-магазин женских сумок, Ташкент</t>
   </si>
@@ -63,7 +68,7 @@
     <t xml:space="preserve">2. «Юнит-экономика» — по каждой модели: закупка в юанях, розничная цена, доля в продажах. Итог — сколько остаётся с заказа и точка безубыточности (колонка «Средняя по долям»).</t>
   </si>
   <si>
-    <t xml:space="preserve">3. «Прогноз» — введите план выкупленных заказов по месяцам и долю постоянных расходов на старте: увидите прибыль по месяцам, окупаемость и сколько денег нужно с учётом закупок товара.</t>
+    <t xml:space="preserve">3. «Прогноз» — введите план выкупленных заказов (без возвратов) по месяцам, долю постоянных расходов на старте, стартовые вложения и первую партию (B19:B26), запас товара в месяцах продаж (B36): увидите прибыль по месяцам, окупаемость и сколько денег нужно с учётом закупок товара.</t>
   </si>
   <si>
     <t xml:space="preserve">4. «Чувствительность» — сколько заказов в месяц нужно при другой цене и другой стоимости рекламы.</t>
@@ -84,7 +89,7 @@
     <t xml:space="preserve">Обозначения</t>
   </si>
   <si>
-    <t xml:space="preserve">Синий текст на жёлтом фоне — ячейки для ввода. Синий текст без заливки — дополнительные настройки (названия месяцев, сдвиги цены на листе «Чувствительность»).</t>
+    <t xml:space="preserve">Синий текст на жёлтом фоне — ячейки для ввода. Синий текст на сером фоне — дополнительные настройки: названия месяцев на листе «Прогноз» и сдвиги цены в строке 10 листа «Чувствительность».</t>
   </si>
   <si>
     <t xml:space="preserve">Чёрный текст — формулы, не трогайте. Зелёный — ссылка на другой лист.</t>
@@ -135,7 +140,7 @@
     <t xml:space="preserve">Допущения: общие для всех моделей</t>
   </si>
   <si>
-    <t xml:space="preserve">Синие цифры на жёлтом фоне — вводите свои значения. Остальные листы пересчитаются сами; на листе «Прогноз» отдельно вводятся план заказов и доля расходов в первые месяцы.</t>
+    <t xml:space="preserve">Синие цифры на жёлтом фоне — вводите свои значения. Остальные листы пересчитаются сами; на листе «Прогноз» отдельно вводятся план заказов, доля расходов в первые месяцы, стартовые вложения и запас товара.</t>
   </si>
   <si>
     <t xml:space="preserve">Параметр</t>
@@ -297,7 +302,7 @@
     <t xml:space="preserve">Возвраты после покупки</t>
   </si>
   <si>
-    <t xml:space="preserve">В бизнес-плане 0%. Возврат = две поездки курьера, сумка возвращается на склад. Поставьте свою оценку, например 2–3%.</t>
+    <t xml:space="preserve">В бизнес-плане 0%. Возврат = две поездки курьера, сумка возвращается на склад. Поставьте свою оценку, например 2–3%. Все расчёты ведутся на заказ, оставшийся у клиентки: в «Прогнозе» вводите заказы за вычетом возвратов.</t>
   </si>
   <si>
     <t xml:space="preserve">Налог с оборота (ИП)</t>
@@ -318,7 +323,7 @@
     <t xml:space="preserve">Реклама на один выкупленный заказ (CAC)</t>
   </si>
   <si>
-    <t xml:space="preserve">Допущение: таргет, блогеры, посевы в Telegram. Рекламный бюджет / число выкупленных заказов (без отказов). Если делите на все заявки — разделите результат на (1 − доля отказов).</t>
+    <t xml:space="preserve">Допущение: таргет, блогеры, посевы в Telegram. Рекламный бюджет / число выкупленных заказов без отказов и возвратов. Если делите на все заявки — разделите результат на (1 − доля отказов) × (1 − доля возвратов).</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссия Uzum Market</t>
@@ -390,7 +395,7 @@
     <t xml:space="preserve">Юнит-экономика: сколько остаётся с одной сумки</t>
   </si>
   <si>
-    <t xml:space="preserve">Суммы в сумах на одну сумку (один выкупленный заказ). Синие ячейки — ввод, чёрные — формулы, зелёные — ссылки на другие листы.</t>
+    <t xml:space="preserve">Суммы в сумах на одну сумку (один выкупленный заказ, который не вернули). Синие ячейки — ввод, чёрные — формулы, зелёные — ссылки на другие листы.</t>
   </si>
   <si>
     <t xml:space="preserve">Показатель</t>
@@ -507,7 +512,7 @@
     <t xml:space="preserve">Отказы и возвраты</t>
   </si>
   <si>
-    <t xml:space="preserve">лишние поездки курьера: отказ у двери — одна, возврат после покупки — две</t>
+    <t xml:space="preserve">лишние поездки курьера: отказ у двери — одна, возврат после покупки — две; на заказ, оставшийся у клиентки</t>
   </si>
   <si>
     <t xml:space="preserve">Налог с оборота</t>
@@ -600,16 +605,16 @@
     <t xml:space="preserve">при 30 днях в месяце</t>
   </si>
   <si>
-    <t xml:space="preserve">Предел для налога с оборота 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выше — оборот больше 1 млрд сум в год: вместо налога 1% — НДС 12% и налог на прибыль, с заказа остаётся меньше</t>
+    <t xml:space="preserve">Предел для налога с оборота (ИП)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выше — оборот больше 1 млрд сум в год: вместо налога с оборота — НДС 12% и налог на прибыль, с заказа остаётся меньше</t>
   </si>
   <si>
     <t xml:space="preserve">Прогноз на 12 месяцев: заказы → прибыль → деньги</t>
   </si>
   <si>
-    <t xml:space="preserve">Вводите выкупленные заказы по месяцам и долю постоянных расходов (жёлтые ячейки). Постоянные расходы берутся из «Допущений»; цена, себестоимость и расходы на заказ — из колонки «Средняя по долям» листа «Юнит-экономика».</t>
+    <t xml:space="preserve">Жёлтые ячейки — ввод: выкупленные заказы (без возвратов) и доля постоянных расходов по месяцам, стартовые вложения и первая партия (B19:B26), запас товара (B36). Постоянные расходы берутся из «Допущений»; цена, себестоимость и расходы на заказ — из колонки «Средняя по долям» листа «Юнит-экономика».</t>
   </si>
   <si>
     <t xml:space="preserve">янв 2027</t>
@@ -651,7 +656,7 @@
     <t xml:space="preserve">Итого за год</t>
   </si>
   <si>
-    <t xml:space="preserve">Выкупленных заказов в месяц</t>
+    <t xml:space="preserve">Выкупленных заказов в месяц (без возвратов)</t>
   </si>
   <si>
     <t xml:space="preserve">Постоянные расходы, сум</t>
@@ -684,9 +689,6 @@
     <t xml:space="preserve">Месяцев с прибылью</t>
   </si>
   <si>
-    <t xml:space="preserve">Налог с оборота 1%: порог 1 млрд сум в год</t>
-  </si>
-  <si>
     <t xml:space="preserve">Стартовые вложения (до запуска)</t>
   </si>
   <si>
@@ -795,10 +797,10 @@
     <t xml:space="preserve">Ячейка в жирной рамке (цена 0%, реклама из «Юнит-экономики») — базовый расчёт. Зелёное — нужно меньше заказов, красное — больше.</t>
   </si>
   <si>
-    <t xml:space="preserve">Сдвиги цены в строке 10 можно менять. Шкала рекламы строится вокруг текущей рекламы с шагом 10 000 сум.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Серым курсивом — оборот выше 1 млрд сум в год: налог 1% уже не действует, реальная точка безубыточности выше.</t>
+    <t xml:space="preserve">Сдвиги цены в строке 10 можно менять. Шкала рекламы строится вокруг текущей рекламы с шагом 10 000 сум; строки с отрицательной рекламой не показываются.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Серым курсивом — оборот выше 1 млрд сум в год: налог с оборота уже не действует, реальная точка безубыточности выше.</t>
   </si>
   <si>
     <t xml:space="preserve">Для Uzum Market реклама в шкале — в сумах на заказ при текущей цене.</t>
@@ -808,18 +810,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\–"/>
+    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;\(#,##0.0\);\–"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;\(#,##0.00\);\–"/>
-    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\–"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="#,##0.0"/>
-    <numFmt numFmtId="172" formatCode="0%"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="\+0%;\-0%;0%"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\–"/>
+    <numFmt numFmtId="170" formatCode="0.0%;\(0.0%\);\–"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0"/>
+    <numFmt numFmtId="173" formatCode="0%"/>
+    <numFmt numFmtId="174" formatCode="0.0"/>
+    <numFmt numFmtId="175" formatCode="\+0%;\-0%;0%"/>
+    <numFmt numFmtId="176" formatCode="#,##0"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1041,7 +1045,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1082,27 +1086,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1110,14 +1122,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1142,7 +1146,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1150,75 +1158,103 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="173" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1226,23 +1262,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1554,7 +1594,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF808080"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1578,17 +1618,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1606,12 +1646,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1629,7 +1669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="4" t="s">
         <v>12</v>
@@ -1673,7 +1713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
         <v>20</v>
       </c>
@@ -1719,7 +1759,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1731,14 +1771,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="84"/>
   </cols>
   <sheetData>
@@ -1774,7 +1814,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>35</v>
       </c>
@@ -1894,7 +1934,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>59</v>
       </c>
@@ -1951,7 +1991,7 @@
       <c r="B21" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="11" t="s">
         <v>71</v>
       </c>
       <c r="D21" s="11" t="s">
@@ -2000,7 +2040,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
         <v>82</v>
       </c>
@@ -2056,7 +2096,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
         <v>91</v>
       </c>
@@ -2084,7 +2124,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
         <v>95</v>
       </c>
@@ -2120,7 +2160,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
         <v>101</v>
       </c>
@@ -2201,17 +2241,17 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="18" t="n">
+      <c r="B41" s="17" t="n">
         <f aca="false">SUM(B34:B40)</f>
         <v>17000000</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="18" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2224,7 +2264,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2236,7 +2276,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF4472C4"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -2310,7 +2350,7 @@
       <c r="A6" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>126</v>
       </c>
       <c r="C6" s="13" t="n">
@@ -2340,25 +2380,25 @@
       <c r="A7" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="25" t="n">
         <v>449000</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="25" t="n">
         <v>549000</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="25" t="n">
         <v>549000</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="25" t="n">
         <v>599000</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="25" t="n">
         <v>649000</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="26" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C7:G7)/$H$8)</f>
         <v>559000</v>
       </c>
@@ -2370,7 +2410,7 @@
       <c r="A8" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="12" t="n">
@@ -2388,11 +2428,11 @@
       <c r="G8" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="27" t="n">
         <f aca="false">SUM(C8:G8)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="16" t="str">
+      <c r="I8" s="18" t="str">
         <f aca="false">IF(H8=0,"Задайте доли продаж моделей",IF(ABS(H8-1)&gt;0.001,"Доли в сумме "&amp;TEXT(H8,"0%")&amp;" — средняя считается пропорционально долям; проверьте ввод","Доли в сумме 100% — всё верно"))</f>
         <v>Доли в сумме 100% — всё верно</v>
       </c>
@@ -2414,30 +2454,30 @@
       <c r="A10" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="29" t="n">
         <f aca="false">C6*Допущения!$B$7</f>
         <v>107250</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="29" t="n">
         <f aca="false">D6*Допущения!$B$7</f>
         <v>156750</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="29" t="n">
         <f aca="false">E6*Допущения!$B$7</f>
         <v>148500</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="29" t="n">
         <f aca="false">F6*Допущения!$B$7</f>
         <v>165000</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="29" t="n">
         <f aca="false">G6*Допущения!$B$7</f>
         <v>206250</v>
       </c>
-      <c r="H10" s="25" t="n">
+      <c r="H10" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C10:G10)/$H$8)</f>
         <v>157162.5</v>
       </c>
@@ -2449,30 +2489,30 @@
       <c r="A11" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="29" t="n">
         <f aca="false">C10*Допущения!$B$10+(C10+C12)*Допущения!$B$11</f>
         <v>5362.5</v>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="29" t="n">
         <f aca="false">D10*Допущения!$B$10+(D10+D12)*Допущения!$B$11</f>
         <v>7837.5</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="29" t="n">
         <f aca="false">E10*Допущения!$B$10+(E10+E12)*Допущения!$B$11</f>
         <v>7425</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="29" t="n">
         <f aca="false">F10*Допущения!$B$10+(F10+F12)*Допущения!$B$11</f>
         <v>8250</v>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="29" t="n">
         <f aca="false">G10*Допущения!$B$10+(G10+G12)*Допущения!$B$11</f>
         <v>10312.5</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C11:G11)/$H$8)</f>
         <v>7858.125</v>
       </c>
@@ -2484,30 +2524,30 @@
       <c r="A12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="29" t="n">
         <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="29" t="n">
         <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="29" t="n">
         <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="29" t="n">
         <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="29" t="n">
         <f aca="false">Допущения!$B$12*Допущения!$B$7</f>
         <v>23100</v>
       </c>
-      <c r="H12" s="25" t="n">
+      <c r="H12" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C12:G12)/$H$8)</f>
         <v>23100</v>
       </c>
@@ -2519,30 +2559,30 @@
       <c r="A13" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="29" t="n">
         <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="29" t="n">
         <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="29" t="n">
         <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="29" t="n">
         <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="29" t="n">
         <f aca="false">Допущения!$B$13*Допущения!$B$6</f>
         <v>40120</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H13" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C13:G13)/$H$8)</f>
         <v>40120</v>
       </c>
@@ -2551,33 +2591,33 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">C10+C12+C13</f>
         <v>170470</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="33" t="n">
         <f aca="false">D10+D12+D13</f>
         <v>219970</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="33" t="n">
         <f aca="false">E10+E12+E13</f>
         <v>211720</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="33" t="n">
         <f aca="false">F10+F12+F13</f>
         <v>228220</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="33" t="n">
         <f aca="false">G10+G12+G13</f>
         <v>269470</v>
       </c>
-      <c r="H14" s="30" t="n">
+      <c r="H14" s="34" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C14:G14)/$H$8)</f>
         <v>220382.5</v>
       </c>
@@ -2589,30 +2629,30 @@
       <c r="A15" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="29" t="n">
         <f aca="false">MAX(C14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>34094</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="29" t="n">
         <f aca="false">MAX(D14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>43994</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="29" t="n">
         <f aca="false">MAX(E14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>42344</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="29" t="n">
         <f aca="false">MAX(F14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>45644</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="29" t="n">
         <f aca="false">MAX(G14*Допущения!$B$14,Допущения!$B$15*Допущения!$B$6)</f>
         <v>53894</v>
       </c>
-      <c r="H15" s="25" t="n">
+      <c r="H15" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C15:G15)/$H$8)</f>
         <v>44076.5</v>
       </c>
@@ -2624,30 +2664,30 @@
       <c r="A16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="29" t="n">
         <f aca="false">(C14+C15)*Допущения!$B$16</f>
         <v>24547.68</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="29" t="n">
         <f aca="false">(D14+D15)*Допущения!$B$16</f>
         <v>31675.68</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="29" t="n">
         <f aca="false">(E14+E15)*Допущения!$B$16</f>
         <v>30487.68</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="29" t="n">
         <f aca="false">(F14+F15)*Допущения!$B$16</f>
         <v>32863.68</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="29" t="n">
         <f aca="false">(G14+G15)*Допущения!$B$16</f>
         <v>38803.68</v>
       </c>
-      <c r="H16" s="25" t="n">
+      <c r="H16" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C16:G16)/$H$8)</f>
         <v>31735.08</v>
       </c>
@@ -2659,30 +2699,30 @@
       <c r="A17" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="29" t="n">
         <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="29" t="n">
         <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="29" t="n">
         <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="29" t="n">
         <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="29" t="n">
         <f aca="false">Допущения!$B$17</f>
         <v>10000</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C17:G17)/$H$8)</f>
         <v>10000</v>
       </c>
@@ -2690,34 +2730,34 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="36" t="n">
         <f aca="false">(C10+C11+C12+C13+C15+C16+C17)/(1-Допущения!$B$18)</f>
         <v>244474.18</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="36" t="n">
         <f aca="false">(D10+D11+D12+D13+D15+D16+D17)/(1-Допущения!$B$18)</f>
         <v>313477.18</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="36" t="n">
         <f aca="false">(E10+E11+E12+E13+E15+E16+E17)/(1-Допущения!$B$18)</f>
         <v>301976.68</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="36" t="n">
         <f aca="false">(F10+F11+F12+F13+F15+F16+F17)/(1-Допущения!$B$18)</f>
         <v>324977.68</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="36" t="n">
         <f aca="false">(G10+G11+G12+G13+G15+G16+G17)/(1-Допущения!$B$18)</f>
         <v>382480.18</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="36" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C18:G18)/$H$8)</f>
         <v>314052.205</v>
       </c>
@@ -2742,30 +2782,30 @@
       <c r="A20" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="29" t="n">
         <f aca="false">C7*(1-Допущения!$B$22)</f>
         <v>449000</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="29" t="n">
         <f aca="false">D7*(1-Допущения!$B$22)</f>
         <v>549000</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="29" t="n">
         <f aca="false">E7*(1-Допущения!$B$22)</f>
         <v>549000</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="29" t="n">
         <f aca="false">F7*(1-Допущения!$B$22)</f>
         <v>599000</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="29" t="n">
         <f aca="false">G7*(1-Допущения!$B$22)</f>
         <v>649000</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C20:G20)/$H$8)</f>
         <v>559000</v>
       </c>
@@ -2777,30 +2817,30 @@
       <c r="A21" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",Допущения!$B$30,Допущения!$B$23)</f>
         <v>30000</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="H21" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C21:G21)/$H$8)</f>
         <v>30000</v>
       </c>
@@ -2808,34 +2848,34 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="27" t="n">
-        <f aca="false">C21*Допущения!$B$24+2*C21*Допущения!$B$25/(1-Допущения!$B$25)</f>
+      <c r="C22" s="29" t="n">
+        <f aca="false">C21*(Допущения!$B$24+2*Допущения!$B$25)/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
-      <c r="D22" s="27" t="n">
-        <f aca="false">D21*Допущения!$B$24+2*D21*Допущения!$B$25/(1-Допущения!$B$25)</f>
+      <c r="D22" s="29" t="n">
+        <f aca="false">D21*(Допущения!$B$24+2*Допущения!$B$25)/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
-      <c r="E22" s="27" t="n">
-        <f aca="false">E21*Допущения!$B$24+2*E21*Допущения!$B$25/(1-Допущения!$B$25)</f>
+      <c r="E22" s="29" t="n">
+        <f aca="false">E21*(Допущения!$B$24+2*Допущения!$B$25)/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
-      <c r="F22" s="27" t="n">
-        <f aca="false">F21*Допущения!$B$24+2*F21*Допущения!$B$25/(1-Допущения!$B$25)</f>
+      <c r="F22" s="29" t="n">
+        <f aca="false">F21*(Допущения!$B$24+2*Допущения!$B$25)/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
-      <c r="G22" s="27" t="n">
-        <f aca="false">G21*Допущения!$B$24+2*G21*Допущения!$B$25/(1-Допущения!$B$25)</f>
+      <c r="G22" s="29" t="n">
+        <f aca="false">G21*(Допущения!$B$24+2*Допущения!$B$25)/(1-Допущения!$B$25)</f>
         <v>2400</v>
       </c>
-      <c r="H22" s="25" t="n">
+      <c r="H22" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C22:G22)/$H$8)</f>
         <v>2400</v>
       </c>
@@ -2847,30 +2887,30 @@
       <c r="A23" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="29" t="n">
         <f aca="false">C20*Допущения!$B$26</f>
         <v>4490</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="29" t="n">
         <f aca="false">D20*Допущения!$B$26</f>
         <v>5490</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="29" t="n">
         <f aca="false">E20*Допущения!$B$26</f>
         <v>5490</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="29" t="n">
         <f aca="false">F20*Допущения!$B$26</f>
         <v>5990</v>
       </c>
-      <c r="G23" s="27" t="n">
+      <c r="G23" s="29" t="n">
         <f aca="false">G20*Допущения!$B$26</f>
         <v>6490</v>
       </c>
-      <c r="H23" s="25" t="n">
+      <c r="H23" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C23:G23)/$H$8)</f>
         <v>5590</v>
       </c>
@@ -2882,30 +2922,30 @@
       <c r="A24" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",0,C20*Допущения!$B$27)</f>
         <v>4490</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",0,D20*Допущения!$B$27)</f>
         <v>5490</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",0,E20*Допущения!$B$27)</f>
         <v>5490</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",0,F20*Допущения!$B$27)</f>
         <v>5990</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",0,G20*Допущения!$B$27)</f>
         <v>6490</v>
       </c>
-      <c r="H24" s="25" t="n">
+      <c r="H24" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C24:G24)/$H$8)</f>
         <v>5590</v>
       </c>
@@ -2917,30 +2957,30 @@
       <c r="A25" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",C20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",D20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",E20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",F20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G25" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",G20*Допущения!$B$29,0)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="25" t="n">
+      <c r="H25" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C25:G25)/$H$8)</f>
         <v>0</v>
       </c>
@@ -2948,34 +2988,34 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",C20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",D20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",E20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",F20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="29" t="n">
         <f aca="false">IF(Допущения!$B$21="Uzum Market",G20*Допущения!$B$31,Допущения!$B$28)</f>
         <v>70000</v>
       </c>
-      <c r="H26" s="25" t="n">
+      <c r="H26" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C26:G26)/$H$8)</f>
         <v>70000</v>
       </c>
@@ -2984,33 +3024,33 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="36" t="n">
         <f aca="false">SUM(C21:C26)</f>
         <v>111380</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="36" t="n">
         <f aca="false">SUM(D21:D26)</f>
         <v>113380</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="36" t="n">
         <f aca="false">SUM(E21:E26)</f>
         <v>113380</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="36" t="n">
         <f aca="false">SUM(F21:F26)</f>
         <v>114380</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="36" t="n">
         <f aca="false">SUM(G21:G26)</f>
         <v>115380</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="36" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C27:G27)/$H$8)</f>
         <v>113580</v>
       </c>
@@ -3032,33 +3072,33 @@
       <c r="I28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="36" t="n">
         <f aca="false">C20-C18-C27</f>
         <v>93145.82</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="36" t="n">
         <f aca="false">D20-D18-D27</f>
         <v>122142.82</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="36" t="n">
         <f aca="false">E20-E18-E27</f>
         <v>133643.32</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F29" s="36" t="n">
         <f aca="false">F20-F18-F27</f>
         <v>159642.32</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="36" t="n">
         <f aca="false">G20-G18-G27</f>
         <v>151139.82</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H29" s="36" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C29:G29)/$H$8)</f>
         <v>131367.795</v>
       </c>
@@ -3070,30 +3110,30 @@
       <c r="A30" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="37" t="n">
         <f aca="false">IFERROR(C29/C20,0)</f>
         <v>0.207451714922049</v>
       </c>
-      <c r="D30" s="32" t="n">
+      <c r="D30" s="37" t="n">
         <f aca="false">IFERROR(D29/D20,0)</f>
         <v>0.222482367941712</v>
       </c>
-      <c r="E30" s="32" t="n">
+      <c r="E30" s="37" t="n">
         <f aca="false">IFERROR(E29/E20,0)</f>
         <v>0.243430455373406</v>
       </c>
-      <c r="F30" s="32" t="n">
+      <c r="F30" s="37" t="n">
         <f aca="false">IFERROR(F29/F20,0)</f>
         <v>0.266514724540902</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="37" t="n">
         <f aca="false">IFERROR(G29/G20,0)</f>
         <v>0.232881078582435</v>
       </c>
-      <c r="H30" s="33" t="n">
+      <c r="H30" s="38" t="n">
         <f aca="false">IFERROR(H29/H20,0)</f>
         <v>0.235005</v>
       </c>
@@ -3105,30 +3145,30 @@
       <c r="A31" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C31" s="34" t="n">
+      <c r="C31" s="39" t="n">
         <f aca="false">IFERROR(C20/C18,0)</f>
         <v>1.83659476841276</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="39" t="n">
         <f aca="false">IFERROR(D20/D18,0)</f>
         <v>1.75132365296893</v>
       </c>
-      <c r="E31" s="34" t="n">
+      <c r="E31" s="39" t="n">
         <f aca="false">IFERROR(E20/E18,0)</f>
         <v>1.81802117964871</v>
       </c>
-      <c r="F31" s="34" t="n">
+      <c r="F31" s="39" t="n">
         <f aca="false">IFERROR(F20/F18,0)</f>
         <v>1.8432035086225</v>
       </c>
-      <c r="G31" s="34" t="n">
+      <c r="G31" s="39" t="n">
         <f aca="false">IFERROR(G20/G18,0)</f>
         <v>1.69681995025206</v>
       </c>
-      <c r="H31" s="35" t="n">
+      <c r="H31" s="40" t="n">
         <f aca="false">IFERROR(H20/H18,0)</f>
         <v>1.77995884474048</v>
       </c>
@@ -3140,30 +3180,30 @@
       <c r="A32" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="29" t="n">
         <f aca="false">C29+C26</f>
         <v>163145.82</v>
       </c>
-      <c r="D32" s="27" t="n">
+      <c r="D32" s="29" t="n">
         <f aca="false">D29+D26</f>
         <v>192142.82</v>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="29" t="n">
         <f aca="false">E29+E26</f>
         <v>203643.32</v>
       </c>
-      <c r="F32" s="27" t="n">
+      <c r="F32" s="29" t="n">
         <f aca="false">F29+F26</f>
         <v>229642.32</v>
       </c>
-      <c r="G32" s="27" t="n">
+      <c r="G32" s="29" t="n">
         <f aca="false">G29+G26</f>
         <v>221139.82</v>
       </c>
-      <c r="H32" s="25" t="n">
+      <c r="H32" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C32:G32)/$H$8)</f>
         <v>201367.795</v>
       </c>
@@ -3175,30 +3215,30 @@
       <c r="A33" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="29" t="n">
         <f aca="false">IFERROR((C18+C21+C22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>353953.244897959</v>
       </c>
-      <c r="D33" s="27" t="n">
+      <c r="D33" s="29" t="n">
         <f aca="false">IFERROR((D18+D21+D22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>424364.469387755</v>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="29" t="n">
         <f aca="false">IFERROR((E18+E21+E22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>412629.265306122</v>
       </c>
-      <c r="F33" s="27" t="n">
+      <c r="F33" s="29" t="n">
         <f aca="false">IFERROR((F18+F21+F22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>436099.673469388</v>
       </c>
-      <c r="G33" s="27" t="n">
+      <c r="G33" s="29" t="n">
         <f aca="false">IFERROR((G18+G21+G22+IF(Допущения!$B$21="Uzum Market",0,Допущения!$B$28))/(1-Допущения!$B$26-IF(Допущения!$B$21="Uzum Market",Допущения!$B$29+Допущения!$B$31,Допущения!$B$27))/(1-Допущения!$B$22),0)</f>
         <v>494775.693877551</v>
       </c>
-      <c r="H33" s="25" t="n">
+      <c r="H33" s="30" t="n">
         <f aca="false">IF($H$8=0,0,SUMPRODUCT($C$8:$G$8,C33:G33)/$H$8)</f>
         <v>424951.229591837</v>
       </c>
@@ -3223,10 +3263,10 @@
       <c r="A36" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="36" t="n">
+      <c r="H36" s="41" t="n">
         <f aca="false">Допущения!$B$41</f>
         <v>17000000</v>
       </c>
@@ -3235,13 +3275,13 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="H37" s="37" t="n">
+      <c r="H37" s="43" t="n">
         <f aca="false">IF($H$8=0,"задайте доли",IF(ROUND(H29,0)&lt;=0,"убыток с заказа",H36/H29))</f>
         <v>129.407667990469</v>
       </c>
@@ -3253,10 +3293,10 @@
       <c r="A38" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="H38" s="38" t="n">
+      <c r="H38" s="44" t="n">
         <f aca="false">IF(ISNUMBER(H37),H37/30,"—")</f>
         <v>4.31358893301564</v>
       </c>
@@ -3265,13 +3305,13 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="H39" s="39" t="n">
+      <c r="H39" s="46" t="n">
         <f aca="false">IF(H20&gt;0,1000000000/12/H20,"—")</f>
         <v>149.075730471079</v>
       </c>
@@ -3297,7 +3337,7 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3310,12 +3350,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF70AD47"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15"/>
   </cols>
@@ -3331,7 +3371,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="40" t="str">
+      <c r="A3" s="47" t="str">
         <f aca="false">IF('Юнит-экономика'!$H$8=0,"Внимание: на листе «Юнит-экономика» не заданы доли продаж моделей (строка 8)","")</f>
         <v/>
       </c>
@@ -3340,40 +3380,40 @@
       <c r="A4" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="48" t="s">
         <v>199</v>
       </c>
       <c r="N4" s="20" t="s">
@@ -3384,43 +3424,43 @@
       <c r="A5" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="25" t="n">
         <v>260</v>
       </c>
-      <c r="N5" s="25" t="n">
+      <c r="N5" s="26" t="n">
         <f aca="false">SUM(B5:M5)</f>
         <v>1670</v>
       </c>
@@ -3429,55 +3469,55 @@
       <c r="A6" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="49" t="n">
         <f aca="false">B7*Допущения!$B$41</f>
         <v>10000000</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="49" t="n">
         <f aca="false">C7*Допущения!$B$41</f>
         <v>10000000</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="49" t="n">
         <f aca="false">D7*Допущения!$B$41</f>
         <v>10000000</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="49" t="n">
         <f aca="false">E7*Допущения!$B$41</f>
         <v>14000000</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="49" t="n">
         <f aca="false">F7*Допущения!$B$41</f>
         <v>14000000</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="49" t="n">
         <f aca="false">G7*Допущения!$B$41</f>
         <v>14000000</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="49" t="n">
         <f aca="false">H7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="49" t="n">
         <f aca="false">I7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="49" t="n">
         <f aca="false">J7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="K6" s="27" t="n">
+      <c r="K6" s="49" t="n">
         <f aca="false">K7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="L6" s="27" t="n">
+      <c r="L6" s="49" t="n">
         <f aca="false">L7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="49" t="n">
         <f aca="false">M7*Допущения!$B$41</f>
         <v>17000000</v>
       </c>
-      <c r="N6" s="25" t="n">
+      <c r="N6" s="26" t="n">
         <f aca="false">SUM(B6:M6)</f>
         <v>174000000</v>
       </c>
@@ -3486,40 +3526,40 @@
       <c r="A7" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="50" t="n">
         <v>0.588235294117647</v>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="50" t="n">
         <v>0.588235294117647</v>
       </c>
-      <c r="D7" s="42" t="n">
+      <c r="D7" s="50" t="n">
         <v>0.588235294117647</v>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E7" s="50" t="n">
         <v>0.823529411764706</v>
       </c>
-      <c r="F7" s="42" t="n">
+      <c r="F7" s="50" t="n">
         <v>0.823529411764706</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="50" t="n">
         <v>0.823529411764706</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="42" t="n">
+      <c r="I7" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="42" t="n">
+      <c r="J7" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="42" t="n">
+      <c r="K7" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="42" t="n">
+      <c r="L7" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="42" t="n">
+      <c r="M7" s="50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3527,55 +3567,55 @@
       <c r="A8" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="49" t="n">
         <f aca="false">B5*'Юнит-экономика'!$H$20</f>
         <v>22360000</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="49" t="n">
         <f aca="false">C5*'Юнит-экономика'!$H$20</f>
         <v>39130000</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="49" t="n">
         <f aca="false">D5*'Юнит-экономика'!$H$20</f>
         <v>83850000</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="49" t="n">
         <f aca="false">E5*'Юнит-экономика'!$H$20</f>
         <v>55900000</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="49" t="n">
         <f aca="false">F5*'Юнит-экономика'!$H$20</f>
         <v>67080000</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="49" t="n">
         <f aca="false">G5*'Юнит-экономика'!$H$20</f>
         <v>72670000</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="49" t="n">
         <f aca="false">H5*'Юнит-экономика'!$H$20</f>
         <v>67080000</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="49" t="n">
         <f aca="false">I5*'Юнит-экономика'!$H$20</f>
         <v>78260000</v>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="49" t="n">
         <f aca="false">J5*'Юнит-экономика'!$H$20</f>
         <v>89440000</v>
       </c>
-      <c r="K8" s="27" t="n">
+      <c r="K8" s="49" t="n">
         <f aca="false">K5*'Юнит-экономика'!$H$20</f>
         <v>100620000</v>
       </c>
-      <c r="L8" s="27" t="n">
+      <c r="L8" s="49" t="n">
         <f aca="false">L5*'Юнит-экономика'!$H$20</f>
         <v>111800000</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="49" t="n">
         <f aca="false">M5*'Юнит-экономика'!$H$20</f>
         <v>145340000</v>
       </c>
-      <c r="N8" s="25" t="n">
+      <c r="N8" s="26" t="n">
         <f aca="false">SUM(B8:M8)</f>
         <v>933530000</v>
       </c>
@@ -3584,55 +3624,55 @@
       <c r="A9" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="49" t="n">
         <f aca="false">B5*'Юнит-экономика'!$H$18</f>
         <v>12562088.2</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="49" t="n">
         <f aca="false">C5*'Юнит-экономика'!$H$18</f>
         <v>21983654.35</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="49" t="n">
         <f aca="false">D5*'Юнит-экономика'!$H$18</f>
         <v>47107830.75</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="49" t="n">
         <f aca="false">E5*'Юнит-экономика'!$H$18</f>
         <v>31405220.5</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="49" t="n">
         <f aca="false">F5*'Юнит-экономика'!$H$18</f>
         <v>37686264.6</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="49" t="n">
         <f aca="false">G5*'Юнит-экономика'!$H$18</f>
         <v>40826786.65</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="49" t="n">
         <f aca="false">H5*'Юнит-экономика'!$H$18</f>
         <v>37686264.6</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="49" t="n">
         <f aca="false">I5*'Юнит-экономика'!$H$18</f>
         <v>43967308.7</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="49" t="n">
         <f aca="false">J5*'Юнит-экономика'!$H$18</f>
         <v>50248352.8</v>
       </c>
-      <c r="K9" s="27" t="n">
+      <c r="K9" s="49" t="n">
         <f aca="false">K5*'Юнит-экономика'!$H$18</f>
         <v>56529396.9</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L9" s="49" t="n">
         <f aca="false">L5*'Юнит-экономика'!$H$18</f>
         <v>62810441</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="49" t="n">
         <f aca="false">M5*'Юнит-экономика'!$H$18</f>
         <v>81653573.3</v>
       </c>
-      <c r="N9" s="25" t="n">
+      <c r="N9" s="26" t="n">
         <f aca="false">SUM(B9:M9)</f>
         <v>524467182.35</v>
       </c>
@@ -3641,169 +3681,169 @@
       <c r="A10" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="49" t="n">
         <f aca="false">B5*'Юнит-экономика'!$H$27</f>
         <v>4543200</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="49" t="n">
         <f aca="false">C5*'Юнит-экономика'!$H$27</f>
         <v>7950600</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="49" t="n">
         <f aca="false">D5*'Юнит-экономика'!$H$27</f>
         <v>17037000</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="49" t="n">
         <f aca="false">E5*'Юнит-экономика'!$H$27</f>
         <v>11358000</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="49" t="n">
         <f aca="false">F5*'Юнит-экономика'!$H$27</f>
         <v>13629600</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="49" t="n">
         <f aca="false">G5*'Юнит-экономика'!$H$27</f>
         <v>14765400</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="49" t="n">
         <f aca="false">H5*'Юнит-экономика'!$H$27</f>
         <v>13629600</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="49" t="n">
         <f aca="false">I5*'Юнит-экономика'!$H$27</f>
         <v>15901200</v>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J10" s="49" t="n">
         <f aca="false">J5*'Юнит-экономика'!$H$27</f>
         <v>18172800</v>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K10" s="49" t="n">
         <f aca="false">K5*'Юнит-экономика'!$H$27</f>
         <v>20444400</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L10" s="49" t="n">
         <f aca="false">L5*'Юнит-экономика'!$H$27</f>
         <v>22716000</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="49" t="n">
         <f aca="false">M5*'Юнит-экономика'!$H$27</f>
         <v>29530800</v>
       </c>
-      <c r="N10" s="25" t="n">
+      <c r="N10" s="26" t="n">
         <f aca="false">SUM(B10:M10)</f>
         <v>189678600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <f aca="false">B8-B9-B10</f>
         <v>5254711.8</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <f aca="false">C8-C9-C10</f>
         <v>9195745.65</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">D8-D9-D10</f>
         <v>19705169.25</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">E8-E9-E10</f>
         <v>13136779.5</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">F8-F9-F10</f>
         <v>15764135.4</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">G8-G9-G10</f>
         <v>17077813.35</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="26" t="n">
         <f aca="false">H8-H9-H10</f>
         <v>15764135.4</v>
       </c>
-      <c r="I11" s="25" t="n">
+      <c r="I11" s="26" t="n">
         <f aca="false">I8-I9-I10</f>
         <v>18391491.3</v>
       </c>
-      <c r="J11" s="25" t="n">
+      <c r="J11" s="26" t="n">
         <f aca="false">J8-J9-J10</f>
         <v>21018847.2</v>
       </c>
-      <c r="K11" s="25" t="n">
+      <c r="K11" s="26" t="n">
         <f aca="false">K8-K9-K10</f>
         <v>23646203.1</v>
       </c>
-      <c r="L11" s="25" t="n">
+      <c r="L11" s="26" t="n">
         <f aca="false">L8-L9-L10</f>
         <v>26273559</v>
       </c>
-      <c r="M11" s="25" t="n">
+      <c r="M11" s="26" t="n">
         <f aca="false">M8-M9-M10</f>
         <v>34155626.7</v>
       </c>
-      <c r="N11" s="25" t="n">
+      <c r="N11" s="26" t="n">
         <f aca="false">SUM(B11:M11)</f>
         <v>219384217.65</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="17" t="n">
         <f aca="false">B11-B6</f>
         <v>-4745288.2</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="17" t="n">
         <f aca="false">C11-C6</f>
         <v>-804254.350000002</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">D11-D6</f>
         <v>9705169.25</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">E11-E6</f>
         <v>-863220.5</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="17" t="n">
         <f aca="false">F11-F6</f>
         <v>1764135.4</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="17" t="n">
         <f aca="false">G11-G6</f>
         <v>3077813.35</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="17" t="n">
         <f aca="false">H11-H6</f>
         <v>-1235864.6</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="I12" s="17" t="n">
         <f aca="false">I11-I6</f>
         <v>1391491.3</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="17" t="n">
         <f aca="false">J11-J6</f>
         <v>4018847.2</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K12" s="17" t="n">
         <f aca="false">K11-K6</f>
         <v>6646203.09999999</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="L12" s="17" t="n">
         <f aca="false">L11-L6</f>
         <v>9273559</v>
       </c>
-      <c r="M12" s="18" t="n">
+      <c r="M12" s="17" t="n">
         <f aca="false">M11-M6</f>
         <v>17155626.7</v>
       </c>
-      <c r="N12" s="18" t="n">
+      <c r="N12" s="17" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>45384217.65</v>
       </c>
@@ -3812,51 +3852,51 @@
       <c r="A13" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="49" t="n">
         <f aca="false">B12</f>
         <v>-4745288.2</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="49" t="n">
         <f aca="false">B13+C12</f>
         <v>-5549542.55</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="49" t="n">
         <f aca="false">C13+D12</f>
         <v>4155626.7</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="49" t="n">
         <f aca="false">D13+E12</f>
         <v>3292406.2</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="49" t="n">
         <f aca="false">E13+F12</f>
         <v>5056541.6</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="49" t="n">
         <f aca="false">F13+G12</f>
         <v>8134354.95</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="49" t="n">
         <f aca="false">G13+H12</f>
         <v>6898490.35</v>
       </c>
-      <c r="I13" s="27" t="n">
+      <c r="I13" s="49" t="n">
         <f aca="false">H13+I12</f>
         <v>8289981.64999999</v>
       </c>
-      <c r="J13" s="27" t="n">
+      <c r="J13" s="49" t="n">
         <f aca="false">I13+J12</f>
         <v>12308828.85</v>
       </c>
-      <c r="K13" s="27" t="n">
+      <c r="K13" s="49" t="n">
         <f aca="false">J13+K12</f>
         <v>18955031.95</v>
       </c>
-      <c r="L13" s="27" t="n">
+      <c r="L13" s="49" t="n">
         <f aca="false">K13+L12</f>
         <v>28228590.95</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="49" t="n">
         <f aca="false">L13+M12</f>
         <v>45384217.65</v>
       </c>
@@ -3865,51 +3905,51 @@
       <c r="A14" s="22" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="49" t="n">
         <f aca="false">B8</f>
         <v>22360000</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="49" t="n">
         <f aca="false">B14+C8</f>
         <v>61490000</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="49" t="n">
         <f aca="false">C14+D8</f>
         <v>145340000</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="49" t="n">
         <f aca="false">D14+E8</f>
         <v>201240000</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="49" t="n">
         <f aca="false">E14+F8</f>
         <v>268320000</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">F14+G8</f>
         <v>340990000</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">G14+H8</f>
         <v>408070000</v>
       </c>
-      <c r="I14" s="27" t="n">
+      <c r="I14" s="49" t="n">
         <f aca="false">H14+I8</f>
         <v>486330000</v>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="49" t="n">
         <f aca="false">I14+J8</f>
         <v>575770000</v>
       </c>
-      <c r="K14" s="27" t="n">
+      <c r="K14" s="49" t="n">
         <f aca="false">J14+K8</f>
         <v>676390000</v>
       </c>
-      <c r="L14" s="27" t="n">
+      <c r="L14" s="49" t="n">
         <f aca="false">K14+L8</f>
         <v>788190000</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="49" t="n">
         <f aca="false">L14+M8</f>
         <v>933530000</v>
       </c>
@@ -3918,23 +3958,24 @@
       <c r="A15" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="49" t="n">
         <f aca="false">COUNTIF(B12:M12,"&gt;0")</f>
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="17" t="str">
-        <f aca="false">IF(N8&gt;1000000000,"Оборот превысит 1 млрд сум в "&amp;INDEX(B4:M4,COUNTIF(B14:M14,"&lt;=1000000000")+1)&amp;": с этого месяца ИП платит НДС 12% и налог на прибыль — прибыль в строке 12 завышена","Оборот за год до 1 млрд сум — налог с оборота 1% сохраняется")</f>
+      <c r="A16" s="22" t="str">
+        <f aca="false">"Налог с оборота "&amp;TEXT(Допущения!$B$26,"0%")&amp;": порог 1 млрд сум в год"</f>
+        <v>Налог с оборота 1%: порог 1 млрд сум в год</v>
+      </c>
+      <c r="B16" s="16" t="str">
+        <f aca="false">IF(N8&gt;1000000000,"Оборот с начала года превысит 1 млрд сум в месяце «"&amp;INDEX(B4:M4,COUNTIF(B14:M14,"&lt;=1000000000")+1)&amp;"»: с этого месяца ИП платит НДС 12% и налог на прибыль — прибыль в строке 12 завышена","Оборот за год до 1 млрд сум — налог с оборота "&amp;TEXT(Допущения!$B$26,"0%")&amp;" сохраняется")</f>
         <v>Оборот за год до 1 млрд сум — налог с оборота 1% сохраняется</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>129</v>
@@ -3942,213 +3983,217 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="10" t="n">
+        <v>213</v>
+      </c>
+      <c r="B19" s="25" t="n">
         <v>6500000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="B20" s="25" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="10" t="n">
+        <v>215</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="10" t="n">
+        <v>216</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="B23" s="10" t="n">
+        <v>217</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <v>18000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="26" t="n">
         <f aca="false">SUM(B19:B24)</f>
         <v>50500000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="47" t="str">
+        <f aca="false">IF(B26&lt;B5,"Первая партия меньше заказов января — увеличьте партию: товар идёт из Китая около 12 недель","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="B27" s="27" t="n">
+        <v>221</v>
+      </c>
+      <c r="B27" s="49" t="n">
         <f aca="false">B26*'Юнит-экономика'!$H$18</f>
         <v>62810441</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="32" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="17" t="n">
         <f aca="false">B25+B27</f>
         <v>113310441</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="B30" s="25" t="n">
+      <c r="A30" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="26" t="n">
         <f aca="false">B13-$B$25</f>
         <v>-55245288.2</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="26" t="n">
         <f aca="false">C13-$B$25</f>
         <v>-56049542.55</v>
       </c>
-      <c r="D30" s="25" t="n">
+      <c r="D30" s="26" t="n">
         <f aca="false">D13-$B$25</f>
         <v>-46344373.3</v>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="26" t="n">
         <f aca="false">E13-$B$25</f>
         <v>-47207593.8</v>
       </c>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="26" t="n">
         <f aca="false">F13-$B$25</f>
         <v>-45443458.4</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="26" t="n">
         <f aca="false">G13-$B$25</f>
         <v>-42365645.05</v>
       </c>
-      <c r="H30" s="25" t="n">
+      <c r="H30" s="26" t="n">
         <f aca="false">H13-$B$25</f>
         <v>-43601509.65</v>
       </c>
-      <c r="I30" s="25" t="n">
+      <c r="I30" s="26" t="n">
         <f aca="false">I13-$B$25</f>
         <v>-42210018.35</v>
       </c>
-      <c r="J30" s="25" t="n">
+      <c r="J30" s="26" t="n">
         <f aca="false">J13-$B$25</f>
         <v>-38191171.15</v>
       </c>
-      <c r="K30" s="25" t="n">
+      <c r="K30" s="26" t="n">
         <f aca="false">K13-$B$25</f>
         <v>-31544968.05</v>
       </c>
-      <c r="L30" s="25" t="n">
+      <c r="L30" s="26" t="n">
         <f aca="false">L13-$B$25</f>
         <v>-22271409.05</v>
       </c>
-      <c r="M30" s="25" t="n">
+      <c r="M30" s="26" t="n">
         <f aca="false">M13-$B$25</f>
         <v>-5115782.35000002</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="43" t="s">
-        <v>226</v>
-      </c>
-      <c r="B31" s="44" t="n">
+      <c r="A31" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="52" t="n">
         <f aca="false">IF(MIN(B30:$M$30)&gt;=0,1,99)</f>
         <v>99</v>
       </c>
-      <c r="C31" s="44" t="n">
+      <c r="C31" s="52" t="n">
         <f aca="false">IF(MIN(C30:$M$30)&gt;=0,2,99)</f>
         <v>99</v>
       </c>
-      <c r="D31" s="44" t="n">
+      <c r="D31" s="52" t="n">
         <f aca="false">IF(MIN(D30:$M$30)&gt;=0,3,99)</f>
         <v>99</v>
       </c>
-      <c r="E31" s="44" t="n">
+      <c r="E31" s="52" t="n">
         <f aca="false">IF(MIN(E30:$M$30)&gt;=0,4,99)</f>
         <v>99</v>
       </c>
-      <c r="F31" s="44" t="n">
+      <c r="F31" s="52" t="n">
         <f aca="false">IF(MIN(F30:$M$30)&gt;=0,5,99)</f>
         <v>99</v>
       </c>
-      <c r="G31" s="44" t="n">
+      <c r="G31" s="52" t="n">
         <f aca="false">IF(MIN(G30:$M$30)&gt;=0,6,99)</f>
         <v>99</v>
       </c>
-      <c r="H31" s="44" t="n">
+      <c r="H31" s="52" t="n">
         <f aca="false">IF(MIN(H30:$M$30)&gt;=0,7,99)</f>
         <v>99</v>
       </c>
-      <c r="I31" s="44" t="n">
+      <c r="I31" s="52" t="n">
         <f aca="false">IF(MIN(I30:$M$30)&gt;=0,8,99)</f>
         <v>99</v>
       </c>
-      <c r="J31" s="44" t="n">
+      <c r="J31" s="52" t="n">
         <f aca="false">IF(MIN(J30:$M$30)&gt;=0,9,99)</f>
         <v>99</v>
       </c>
-      <c r="K31" s="44" t="n">
+      <c r="K31" s="52" t="n">
         <f aca="false">IF(MIN(K30:$M$30)&gt;=0,10,99)</f>
         <v>99</v>
       </c>
-      <c r="L31" s="44" t="n">
+      <c r="L31" s="52" t="n">
         <f aca="false">IF(MIN(L30:$M$30)&gt;=0,11,99)</f>
         <v>99</v>
       </c>
-      <c r="M31" s="44" t="n">
+      <c r="M31" s="52" t="n">
         <f aca="false">IF(MIN(M30:$M$30)&gt;=0,12,99)</f>
         <v>99</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="B32" s="45" t="str">
+      <c r="A32" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" s="53" t="str">
         <f aca="false">IF(MIN(B31:M31)=99,IF(M12&lt;=0,"не окупается: в декабре убыток","позже 12 месяцев"),INDEX(B4:M4,MIN(B31:M31)))</f>
         <v>позже 12 месяцев</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
-        <v>228</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="32" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4164,322 +4209,322 @@
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
     </row>
-    <row r="36" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B36" s="54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C36" s="32" t="s">
         <v>230</v>
-      </c>
-      <c r="B36" s="46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="B37" s="27" t="n">
+        <v>231</v>
+      </c>
+      <c r="B37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(C5*$B$36,0)-($B$26-B5))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="27" t="n">
+      <c r="C37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(D5*$B$36,0)-(B38-C5))</f>
         <v>105</v>
       </c>
-      <c r="D37" s="27" t="n">
+      <c r="D37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(E5*$B$36,0)-(C38-D5))</f>
         <v>85</v>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(F5*$B$36,0)-(D38-E5))</f>
         <v>126</v>
       </c>
-      <c r="F37" s="27" t="n">
+      <c r="F37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(G5*$B$36,0)-(E38-F5))</f>
         <v>133</v>
       </c>
-      <c r="G37" s="27" t="n">
+      <c r="G37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(H5*$B$36,0)-(F38-G5))</f>
         <v>117</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(I5*$B$36,0)-(G38-H5))</f>
         <v>146</v>
       </c>
-      <c r="I37" s="27" t="n">
+      <c r="I37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(J5*$B$36,0)-(H38-I5))</f>
         <v>166</v>
       </c>
-      <c r="J37" s="27" t="n">
+      <c r="J37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(K5*$B$36,0)-(I38-J5))</f>
         <v>186</v>
       </c>
-      <c r="K37" s="27" t="n">
+      <c r="K37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(L5*$B$36,0)-(J38-K5))</f>
         <v>206</v>
       </c>
-      <c r="L37" s="27" t="n">
+      <c r="L37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(M5*$B$36,0)-(K38-L5))</f>
         <v>278</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="49" t="n">
         <f aca="false">MAX(0,ROUND(M5*$B$36,0)-(L38-M5))</f>
         <v>260</v>
       </c>
-      <c r="N37" s="25" t="n">
+      <c r="N37" s="26" t="n">
         <f aca="false">SUM(B37:M37)</f>
         <v>1808</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="B38" s="27" t="n">
+        <v>232</v>
+      </c>
+      <c r="B38" s="49" t="n">
         <f aca="false">$B$26-B5+B37</f>
         <v>160</v>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="49" t="n">
         <f aca="false">B38-C5+C37</f>
         <v>195</v>
       </c>
-      <c r="D38" s="27" t="n">
+      <c r="D38" s="49" t="n">
         <f aca="false">C38-D5+D37</f>
         <v>130</v>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="49" t="n">
         <f aca="false">D38-E5+E37</f>
         <v>156</v>
       </c>
-      <c r="F38" s="27" t="n">
+      <c r="F38" s="49" t="n">
         <f aca="false">E38-F5+F37</f>
         <v>169</v>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G38" s="49" t="n">
         <f aca="false">F38-G5+G37</f>
         <v>156</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="H38" s="49" t="n">
         <f aca="false">G38-H5+H37</f>
         <v>182</v>
       </c>
-      <c r="I38" s="27" t="n">
+      <c r="I38" s="49" t="n">
         <f aca="false">H38-I5+I37</f>
         <v>208</v>
       </c>
-      <c r="J38" s="27" t="n">
+      <c r="J38" s="49" t="n">
         <f aca="false">I38-J5+J37</f>
         <v>234</v>
       </c>
-      <c r="K38" s="27" t="n">
+      <c r="K38" s="49" t="n">
         <f aca="false">J38-K5+K37</f>
         <v>260</v>
       </c>
-      <c r="L38" s="27" t="n">
+      <c r="L38" s="49" t="n">
         <f aca="false">K38-L5+L37</f>
         <v>338</v>
       </c>
-      <c r="M38" s="27" t="n">
+      <c r="M38" s="49" t="n">
         <f aca="false">L38-M5+M37</f>
         <v>338</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="B39" s="27" t="n">
+        <v>233</v>
+      </c>
+      <c r="B39" s="49" t="n">
         <f aca="false">B37*'Юнит-экономика'!$H$18</f>
         <v>0</v>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="49" t="n">
         <f aca="false">C37*'Юнит-экономика'!$H$18</f>
         <v>32975481.525</v>
       </c>
-      <c r="D39" s="27" t="n">
+      <c r="D39" s="49" t="n">
         <f aca="false">D37*'Юнит-экономика'!$H$18</f>
         <v>26694437.425</v>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E39" s="49" t="n">
         <f aca="false">E37*'Юнит-экономика'!$H$18</f>
         <v>39570577.83</v>
       </c>
-      <c r="F39" s="27" t="n">
+      <c r="F39" s="49" t="n">
         <f aca="false">F37*'Юнит-экономика'!$H$18</f>
         <v>41768943.265</v>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="49" t="n">
         <f aca="false">G37*'Юнит-экономика'!$H$18</f>
         <v>36744107.985</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="49" t="n">
         <f aca="false">H37*'Юнит-экономика'!$H$18</f>
         <v>45851621.93</v>
       </c>
-      <c r="I39" s="27" t="n">
+      <c r="I39" s="49" t="n">
         <f aca="false">I37*'Юнит-экономика'!$H$18</f>
         <v>52132666.03</v>
       </c>
-      <c r="J39" s="27" t="n">
+      <c r="J39" s="49" t="n">
         <f aca="false">J37*'Юнит-экономика'!$H$18</f>
         <v>58413710.13</v>
       </c>
-      <c r="K39" s="27" t="n">
+      <c r="K39" s="49" t="n">
         <f aca="false">K37*'Юнит-экономика'!$H$18</f>
         <v>64694754.23</v>
       </c>
-      <c r="L39" s="27" t="n">
+      <c r="L39" s="49" t="n">
         <f aca="false">L37*'Юнит-экономика'!$H$18</f>
         <v>87306512.99</v>
       </c>
-      <c r="M39" s="27" t="n">
+      <c r="M39" s="49" t="n">
         <f aca="false">M37*'Юнит-экономика'!$H$18</f>
         <v>81653573.3</v>
       </c>
-      <c r="N39" s="25" t="n">
+      <c r="N39" s="26" t="n">
         <f aca="false">SUM(B39:M39)</f>
         <v>567806386.64</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="B40" s="27" t="n">
+        <v>234</v>
+      </c>
+      <c r="B40" s="49" t="n">
         <f aca="false">B8-B10-B6-B39</f>
         <v>7816800</v>
       </c>
-      <c r="C40" s="27" t="n">
+      <c r="C40" s="49" t="n">
         <f aca="false">C8-C10-C6-C39</f>
         <v>-11796081.525</v>
       </c>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="49" t="n">
         <f aca="false">D8-D10-D6-D39</f>
         <v>30118562.575</v>
       </c>
-      <c r="E40" s="27" t="n">
+      <c r="E40" s="49" t="n">
         <f aca="false">E8-E10-E6-E39</f>
         <v>-9028577.83000001</v>
       </c>
-      <c r="F40" s="27" t="n">
+      <c r="F40" s="49" t="n">
         <f aca="false">F8-F10-F6-F39</f>
         <v>-2318543.265</v>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="49" t="n">
         <f aca="false">G8-G10-G6-G39</f>
         <v>7160492.015</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H40" s="49" t="n">
         <f aca="false">H8-H10-H6-H39</f>
         <v>-9401221.93</v>
       </c>
-      <c r="I40" s="27" t="n">
+      <c r="I40" s="49" t="n">
         <f aca="false">I8-I10-I6-I39</f>
         <v>-6773866.03</v>
       </c>
-      <c r="J40" s="27" t="n">
+      <c r="J40" s="49" t="n">
         <f aca="false">J8-J10-J6-J39</f>
         <v>-4146510.13</v>
       </c>
-      <c r="K40" s="27" t="n">
+      <c r="K40" s="49" t="n">
         <f aca="false">K8-K10-K6-K39</f>
         <v>-1519154.23</v>
       </c>
-      <c r="L40" s="27" t="n">
+      <c r="L40" s="49" t="n">
         <f aca="false">L8-L10-L6-L39</f>
         <v>-15222512.99</v>
       </c>
-      <c r="M40" s="27" t="n">
+      <c r="M40" s="49" t="n">
         <f aca="false">M8-M10-M6-M39</f>
         <v>17155626.7</v>
       </c>
-      <c r="N40" s="25" t="n">
+      <c r="N40" s="26" t="n">
         <f aca="false">SUM(B40:M40)</f>
         <v>2045013.35999998</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B41" s="25" t="n">
+      <c r="A41" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" s="26" t="n">
         <f aca="false">-$B$28+B40</f>
         <v>-105493641</v>
       </c>
-      <c r="C41" s="25" t="n">
+      <c r="C41" s="26" t="n">
         <f aca="false">B41+C40</f>
         <v>-117289722.525</v>
       </c>
-      <c r="D41" s="25" t="n">
+      <c r="D41" s="26" t="n">
         <f aca="false">C41+D40</f>
         <v>-87171159.95</v>
       </c>
-      <c r="E41" s="25" t="n">
+      <c r="E41" s="26" t="n">
         <f aca="false">D41+E40</f>
         <v>-96199737.78</v>
       </c>
-      <c r="F41" s="25" t="n">
+      <c r="F41" s="26" t="n">
         <f aca="false">E41+F40</f>
         <v>-98518281.045</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="26" t="n">
         <f aca="false">F41+G40</f>
         <v>-91357789.03</v>
       </c>
-      <c r="H41" s="25" t="n">
+      <c r="H41" s="26" t="n">
         <f aca="false">G41+H40</f>
         <v>-100759010.96</v>
       </c>
-      <c r="I41" s="25" t="n">
+      <c r="I41" s="26" t="n">
         <f aca="false">H41+I40</f>
         <v>-107532876.99</v>
       </c>
-      <c r="J41" s="25" t="n">
+      <c r="J41" s="26" t="n">
         <f aca="false">I41+J40</f>
         <v>-111679387.12</v>
       </c>
-      <c r="K41" s="25" t="n">
+      <c r="K41" s="26" t="n">
         <f aca="false">J41+K40</f>
         <v>-113198541.35</v>
       </c>
-      <c r="L41" s="25" t="n">
+      <c r="L41" s="26" t="n">
         <f aca="false">K41+L40</f>
         <v>-128421054.34</v>
       </c>
-      <c r="M41" s="25" t="n">
+      <c r="M41" s="26" t="n">
         <f aca="false">L41+M40</f>
         <v>-111265427.64</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="B43" s="18" t="n">
+      <c r="A43" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" s="17" t="n">
         <f aca="false">MAX($B$28,-MIN(B41:M41))</f>
         <v>128421054.34</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="B44" s="18" t="n">
+      <c r="A44" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B44" s="17" t="n">
         <f aca="false">B43*1.1</f>
         <v>141263159.774</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="B45" s="27" t="n">
+        <v>238</v>
+      </c>
+      <c r="B45" s="49" t="n">
         <f aca="false">M38*'Юнит-экономика'!$H$18</f>
         <v>106149645.29</v>
       </c>
-      <c r="C45" s="24" t="s">
-        <v>240</v>
+      <c r="C45" s="32" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4503,9 +4548,15 @@
       <formula>B40&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" error="Запас меньше 1 месяца: часть товара пришлось бы купить и продать в одном месяце, а путь из Китая около 12 недель" errorStyle="warning" errorTitle="Запас товара" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B36" type="decimal">
+      <formula1>1</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4517,7 +4568,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFED7D31"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -4528,493 +4579,493 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="40" t="str">
+      <c r="A3" s="47" t="str">
         <f aca="false">IF('Юнит-экономика'!$H$8=0,"Внимание: на листе «Юнит-экономика» не заданы доли продаж моделей (строка 8)","")</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="36" t="n">
+      <c r="A4" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="41" t="n">
         <f aca="false">'Юнит-экономика'!$H$20</f>
         <v>559000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="B5" s="36" t="n">
+      <c r="A5" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="41" t="n">
         <f aca="false">'Юнит-экономика'!$H$18</f>
         <v>314052.205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B6" s="36" t="n">
+      <c r="A6" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="41" t="n">
         <f aca="false">'Юнит-экономика'!$H$21+'Юнит-экономика'!$H$22</f>
         <v>32400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="47" t="n">
+      <c r="A7" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="55" t="n">
         <f aca="false">IFERROR(('Юнит-экономика'!$H$23+'Юнит-экономика'!$H$24+'Юнит-экономика'!$H$25)/'Юнит-экономика'!$H$20,0)</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="41" t="n">
         <f aca="false">Допущения!$B$41</f>
         <v>17000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="48" t="n">
+        <v>246</v>
+      </c>
+      <c r="B10" s="56" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="56" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="56" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="56" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G10" s="56" t="n">
         <v>0.05</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="56" t="n">
         <v>0.1</v>
       </c>
-      <c r="I10" s="48" t="n">
+      <c r="I10" s="56" t="n">
         <v>0.15</v>
       </c>
-      <c r="J10" s="48" t="n">
+      <c r="J10" s="56" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="n">
-        <f aca="false">MAX(0,$A$14-30000)</f>
+      <c r="A11" s="57" t="n">
+        <f aca="false">IF($A$14&gt;=30000,$A$14-30000,"")</f>
         <v>40000</v>
       </c>
-      <c r="B11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="B11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>328.161286253256</v>
       </c>
-      <c r="C11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="C11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>214.660572074213</v>
       </c>
-      <c r="D11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="D11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>159.495925324758</v>
       </c>
-      <c r="E11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="E11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>126.887644983596</v>
       </c>
-      <c r="F11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="F11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>105.349397629186</v>
       </c>
-      <c r="G11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="G11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>90.062028632891</v>
       </c>
-      <c r="H11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="H11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>78.6491608747536</v>
       </c>
-      <c r="I11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="I11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>69.8035004771993</v>
       </c>
-      <c r="J11" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11))</f>
+      <c r="J11" s="58" t="n">
+        <f aca="false">IF($A11="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A11)))</f>
         <v>62.7464192602422</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="n">
-        <f aca="false">MAX(0,$A$14-20000)</f>
+      <c r="A12" s="57" t="n">
+        <f aca="false">IF($A$14&gt;=20000,$A$14-20000,"")</f>
         <v>50000</v>
       </c>
-      <c r="B12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="B12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>406.661643996676</v>
       </c>
-      <c r="C12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="C12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>245.68321938088</v>
       </c>
-      <c r="D12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="D12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>176.009318968695</v>
       </c>
-      <c r="E12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="E12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>137.122434887916</v>
       </c>
-      <c r="F12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="F12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>112.309226675331</v>
       </c>
-      <c r="G12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="G12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>95.1002159082578</v>
       </c>
-      <c r="H12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="H12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>82.4643070831092</v>
       </c>
-      <c r="I12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="I12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>72.7924215553004</v>
       </c>
-      <c r="J12" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12))</f>
+      <c r="J12" s="58" t="n">
+        <f aca="false">IF($A12="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A12)))</f>
         <v>65.1511250286689</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="n">
-        <f aca="false">MAX(0,$A$14-10000)</f>
+      <c r="A13" s="57" t="n">
+        <f aca="false">IF($A$14&gt;=10000,$A$14-10000,"")</f>
         <v>60000</v>
       </c>
-      <c r="B13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="B13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>534.527404669789</v>
       </c>
-      <c r="C13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="C13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>287.18741233921</v>
       </c>
-      <c r="D13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="D13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>196.337055056202</v>
       </c>
-      <c r="E13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="E13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>149.153167537304</v>
       </c>
-      <c r="F13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="F13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>120.253697102653</v>
       </c>
-      <c r="G13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="G13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>100.735490556211</v>
       </c>
-      <c r="H13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="H13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>86.6684566252032</v>
       </c>
-      <c r="I13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="I13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>76.0487587959057</v>
       </c>
-      <c r="J13" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13))</f>
+      <c r="J13" s="58" t="n">
+        <f aca="false">IF($A13="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A13)))</f>
         <v>67.7474928994152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="n">
+      <c r="A14" s="59" t="n">
         <f aca="false">'Юнит-экономика'!$H$26</f>
         <v>70000</v>
       </c>
-      <c r="B14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="B14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>779.680784927579</v>
       </c>
-      <c r="C14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="C14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>345.56501353446</v>
       </c>
-      <c r="D14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="D14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>221.973278465021</v>
       </c>
-      <c r="E14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="E14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>163.498018957018</v>
       </c>
-      <c r="F14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="F14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>129.407667990469</v>
       </c>
-      <c r="G14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="G14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>107.080681734829</v>
       </c>
-      <c r="H14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="H14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>91.3243014852635</v>
       </c>
-      <c r="I14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="I14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>79.6100810620285</v>
       </c>
-      <c r="J14" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14))</f>
+      <c r="J14" s="58" t="n">
+        <f aca="false">IF($A14="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A14)))</f>
         <v>70.5593879794902</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="57" t="n">
         <f aca="false">$A$14+10000</f>
         <v>80000</v>
       </c>
-      <c r="B15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="B15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>1440.21477838272</v>
       </c>
-      <c r="C15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="C15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>433.731060463513</v>
       </c>
-      <c r="D15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="D15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>255.309709826248</v>
       </c>
-      <c r="E15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="E15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>180.895720055148</v>
       </c>
-      <c r="F15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="F15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>140.070106736305</v>
       </c>
-      <c r="G15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="G15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>114.278957422316</v>
       </c>
-      <c r="H15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="H15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>96.5087697093261</v>
       </c>
-      <c r="I15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="I15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>83.5213402797213</v>
       </c>
-      <c r="J15" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15))</f>
+      <c r="J15" s="58" t="n">
+        <f aca="false">IF($A15="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A15)))</f>
         <v>73.6148090824826</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="57" t="n">
         <f aca="false">$A$14+20000</f>
         <v>90000</v>
       </c>
-      <c r="B16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="B16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>9424.57430029474</v>
       </c>
-      <c r="C16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="C16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>582.295577002682</v>
       </c>
-      <c r="D16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="D16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>300.428756015534</v>
       </c>
-      <c r="E16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="E16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>202.436875567828</v>
       </c>
-      <c r="F16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="F16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>152.647360935897</v>
       </c>
-      <c r="G16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="G16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>122.514756632183</v>
       </c>
-      <c r="H16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="H16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>102.317309509771</v>
       </c>
-      <c r="I16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="I16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>87.8367788041793</v>
       </c>
-      <c r="J16" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16))</f>
+      <c r="J16" s="58" t="n">
+        <f aca="false">IF($A16="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A16)))</f>
         <v>76.9468242450119</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="57" t="n">
         <f aca="false">$A$14+30000</f>
         <v>100000</v>
       </c>
-      <c r="B17" s="49" t="str">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="B17" s="58" t="str">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>убыток</v>
       </c>
-      <c r="C17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="C17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>885.656762679675</v>
       </c>
-      <c r="D17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="D17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>364.918104327725</v>
       </c>
-      <c r="E17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="E17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>229.801791223856</v>
       </c>
-      <c r="F17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="F17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>167.706124020948</v>
       </c>
-      <c r="G17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="G17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>132.029815905003</v>
       </c>
-      <c r="H17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="H17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>108.869819521697</v>
       </c>
-      <c r="I17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="I17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>92.6224603091645</v>
       </c>
-      <c r="J17" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17))</f>
+      <c r="J17" s="58" t="n">
+        <f aca="false">IF($A17="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A17)))</f>
         <v>80.5947723528357</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="57" t="n">
         <f aca="false">$A$14+40000</f>
         <v>110000</v>
       </c>
-      <c r="B18" s="49" t="str">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="B18" s="58" t="str">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>убыток</v>
       </c>
-      <c r="C18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="C18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>1848.87210644718</v>
       </c>
-      <c r="D18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="D18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>464.661216190601</v>
       </c>
-      <c r="E18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="E18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>265.721344746951</v>
       </c>
-      <c r="F18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="F18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>186.061182717609</v>
       </c>
-      <c r="G18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="G18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>143.147292796294</v>
       </c>
-      <c r="H18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="H18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>116.319013653081</v>
       </c>
-      <c r="I18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="I18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>97.9596757062223</v>
       </c>
-      <c r="J18" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18))</f>
+      <c r="J18" s="58" t="n">
+        <f aca="false">IF($A18="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A18)))</f>
         <v>84.6058235830721</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="57" t="n">
         <f aca="false">$A$14+50000</f>
         <v>120000</v>
       </c>
-      <c r="B19" s="49" t="str">
-        <f aca="false">IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="B19" s="58" t="str">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+B$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>убыток</v>
       </c>
-      <c r="C19" s="49" t="str">
-        <f aca="false">IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="C19" s="58" t="str">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+C$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>убыток</v>
       </c>
-      <c r="D19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="D19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+D$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>639.439219327465</v>
       </c>
-      <c r="E19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="E19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+E$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>314.950155895696</v>
       </c>
-      <c r="F19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="F19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+F$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>208.927868820828</v>
       </c>
-      <c r="G19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="G19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+G$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>156.30919779867</v>
       </c>
-      <c r="H19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="H19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+H$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>124.862472249775</v>
       </c>
-      <c r="I19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="I19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+I$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>103.949598630727</v>
       </c>
-      <c r="J19" s="49" t="n">
-        <f aca="false">IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19))</f>
+      <c r="J19" s="58" t="n">
+        <f aca="false">IF($A19="","",IF(ROUND(($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19),0)&lt;=0,"убыток",$B$8/($B$4*(1+J$10)*(1-$B$7)-$B$5-$B$6-$A19)))</f>
         <v>89.0370302128045</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5033,7 +5084,7 @@
       <formula>B11="убыток"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>AND(B$10=0,$A11=$A$14)</formula>
+      <formula>AND(B$10=0,ROW()=14)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>AND(ISNUMBER(B11),B11*$B$4*(1+B$10)*12&gt;1000000000)</formula>
@@ -5041,7 +5092,7 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
